--- a/public/templates/as_build_template.xlsx
+++ b/public/templates/as_build_template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1567D4A-11A8-4396-9B3E-5581C031494E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9BAC0CE-89B1-4210-BBBC-B2B83DCDCD14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="3030" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51480" yWindow="3030" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ΚΤΗΡΙΟ" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="178">
   <si>
     <t>SRId</t>
   </si>
@@ -103,93 +103,93 @@
     <t>FAILURE</t>
   </si>
   <si>
-    <t>2-340186247156</t>
-  </si>
-  <si>
-    <t>682245537</t>
+    <t>773138</t>
+  </si>
+  <si>
+    <t>682242737</t>
   </si>
   <si>
     <t>OTE</t>
   </si>
   <si>
+    <t>+00</t>
+  </si>
+  <si>
+    <t>BEP 1SP 1:8(01..12) ΚΔ</t>
+  </si>
+  <si>
+    <t>MEDIUM/12/ZTT (01..12)</t>
+  </si>
+  <si>
+    <t>SMALL/16/RAYCAP</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>b24</t>
+  </si>
+  <si>
+    <t>ΟΡΟΦΟΣ</t>
+  </si>
+  <si>
+    <t>ΔΙΑΜΕΡΙΣΜΑΤΑ</t>
+  </si>
+  <si>
+    <t>ΚΑΤΑΣΤΗΜΑΤΑ</t>
+  </si>
+  <si>
+    <t>FB01</t>
+  </si>
+  <si>
+    <t>FB01 TYPE</t>
+  </si>
+  <si>
+    <t>FB02</t>
+  </si>
+  <si>
+    <t>FB02 TYPE</t>
+  </si>
+  <si>
+    <t>FB03</t>
+  </si>
+  <si>
+    <t>FB03 TYPE</t>
+  </si>
+  <si>
+    <t>FB04</t>
+  </si>
+  <si>
+    <t>FB04 TYPE</t>
+  </si>
+  <si>
+    <t>FB ΠΕΛΑΤΗ</t>
+  </si>
+  <si>
+    <t>ΑΡΙΘΜΗΣΗ ΧΩΡΟΥ ΠΕΛΑΤΗ</t>
+  </si>
+  <si>
+    <t>GIS ID</t>
+  </si>
+  <si>
+    <t>FB 4 PORTS</t>
+  </si>
+  <si>
+    <t>FB(+00).1</t>
+  </si>
+  <si>
+    <t>ΙΣ1</t>
+  </si>
+  <si>
     <t>+01</t>
   </si>
   <si>
-    <t>+00</t>
-  </si>
-  <si>
-    <t>BEP 1SP 1:8(01..12) ΚΔ</t>
-  </si>
-  <si>
-    <t>MEDIUM/12/ZTT (01..12)</t>
-  </si>
-  <si>
-    <t>SMALL/16/RAYCAP</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>b08</t>
-  </si>
-  <si>
-    <t>ΟΡΟΦΟΣ</t>
-  </si>
-  <si>
-    <t>ΔΙΑΜΕΡΙΣΜΑΤΑ</t>
-  </si>
-  <si>
-    <t>ΚΑΤΑΣΤΗΜΑΤΑ</t>
-  </si>
-  <si>
-    <t>FB01</t>
-  </si>
-  <si>
-    <t>FB01 TYPE</t>
-  </si>
-  <si>
-    <t>FB02</t>
-  </si>
-  <si>
-    <t>FB02 TYPE</t>
-  </si>
-  <si>
-    <t>FB03</t>
-  </si>
-  <si>
-    <t>FB03 TYPE</t>
-  </si>
-  <si>
-    <t>FB04</t>
-  </si>
-  <si>
-    <t>FB04 TYPE</t>
-  </si>
-  <si>
-    <t>FB ΠΕΛΑΤΗ</t>
-  </si>
-  <si>
-    <t>ΑΡΙΘΜΗΣΗ ΧΩΡΟΥ ΠΕΛΑΤΗ</t>
-  </si>
-  <si>
-    <t>GIS ID</t>
-  </si>
-  <si>
-    <t>FB 4 PORTS</t>
-  </si>
-  <si>
-    <t>+ΗΜ</t>
-  </si>
-  <si>
-    <t>FB(+01).1</t>
-  </si>
-  <si>
-    <t>Α1</t>
-  </si>
-  <si>
     <t>+02</t>
   </si>
   <si>
+    <t>+03</t>
+  </si>
+  <si>
     <t>OPTICAL PATH TYPE</t>
   </si>
   <si>
@@ -202,46 +202,46 @@
     <t>CAB-BEP</t>
   </si>
   <si>
-    <t>G137_B1.2_BEP01(b08)_02</t>
-  </si>
-  <si>
-    <t>G137_B1.3_BEP01(b08)_03</t>
-  </si>
-  <si>
-    <t>G137_B1.4_BEP01(b08)_04</t>
-  </si>
-  <si>
-    <t>G137_SGA01(1:8).01_B1.1_BEP01(b08)_01_SB01(1:8)</t>
+    <t>G137_B1.6_BEP01(b24)_02</t>
+  </si>
+  <si>
+    <t>G137_B1.7_BEP01(b24)_03</t>
+  </si>
+  <si>
+    <t>G137_B1.8_BEP01(b24)_04</t>
+  </si>
+  <si>
+    <t>G137_SGA01(1:8).02_B1.5_BEP01(b24)_01_SB01(1:8)</t>
   </si>
   <si>
     <t>BEP-BMO</t>
   </si>
   <si>
-    <t>BEP01(b08)_SB01(1:8).01_05_BMO01_1</t>
-  </si>
-  <si>
-    <t>BEP01(b08)_SB01(1:8).02_06_BMO01_2</t>
-  </si>
-  <si>
-    <t>BEP01(b08)_SB01(1:8).03_07_BMO01_5</t>
-  </si>
-  <si>
-    <t>BEP01(b08)_SB01(1:8).04_08_BMO01_6</t>
-  </si>
-  <si>
-    <t>BEP01(b08)_SB01(1:8).05_09_BMO01_9</t>
-  </si>
-  <si>
-    <t>BEP01(b08)_SB01(1:8).06_10_BMO01_10</t>
-  </si>
-  <si>
-    <t>BEP01(b08)_SB01(1:8).07_11_BMO01_13</t>
+    <t>BEP01(b24)_SB01(1:8).01_05_BMO01_1</t>
+  </si>
+  <si>
+    <t>BEP01(b24)_SB01(1:8).02_06_BMO01_2</t>
+  </si>
+  <si>
+    <t>BEP01(b24)_SB01(1:8).03_07_BMO01_5</t>
+  </si>
+  <si>
+    <t>BEP01(b24)_SB01(1:8).04_08_BMO01_6</t>
+  </si>
+  <si>
+    <t>BEP01(b24)_SB01(1:8).05_09_BMO01_9</t>
+  </si>
+  <si>
+    <t>BEP01(b24)_SB01(1:8).06_10_BMO01_10</t>
+  </si>
+  <si>
+    <t>BEP01(b24)_SB01(1:8).07_11_BMO01_13</t>
   </si>
   <si>
     <t>BEP</t>
   </si>
   <si>
-    <t>BEP01(b08)_SB01(1:8).08_12</t>
+    <t>BEP01(b24)_SB01(1:8).08_12</t>
   </si>
   <si>
     <t>BMO-FB</t>
@@ -250,19 +250,19 @@
     <t>BMO01_1_FB(+00).1_01</t>
   </si>
   <si>
-    <t>BMO01_10_FB(+01).1_02</t>
-  </si>
-  <si>
-    <t>BMO01_11_FB(+01).1_03</t>
-  </si>
-  <si>
-    <t>BMO01_12_FB(+01).1_04</t>
-  </si>
-  <si>
-    <t>BMO01_13_FB(+02).1_01</t>
-  </si>
-  <si>
-    <t>BMO01_14_FB(+02).1_02</t>
+    <t>BMO01_10_FB(+02).1_02</t>
+  </si>
+  <si>
+    <t>BMO01_11_FB(+02).1_03</t>
+  </si>
+  <si>
+    <t>BMO01_12_FB(+02).1_04</t>
+  </si>
+  <si>
+    <t>BMO01_13_FB(+03).1_01</t>
+  </si>
+  <si>
+    <t>BMO01_14_FB(+03).1_02</t>
   </si>
   <si>
     <t>BMO01_2_FB(+00).1_02</t>
@@ -274,19 +274,19 @@
     <t>BMO01_4_FB(+00).1_04</t>
   </si>
   <si>
-    <t>BMO01_5_FB(+ΗΜ).1_01</t>
-  </si>
-  <si>
-    <t>BMO01_6_FB(+ΗΜ).1_02</t>
-  </si>
-  <si>
-    <t>BMO01_7_FB(+ΗΜ).1_03</t>
-  </si>
-  <si>
-    <t>BMO01_8_FB(+ΗΜ).1_04</t>
-  </si>
-  <si>
-    <t>BMO01_9_FB(+01).1_01</t>
+    <t>BMO01_5_FB(+01).1_01</t>
+  </si>
+  <si>
+    <t>BMO01_6_FB(+01).1_02</t>
+  </si>
+  <si>
+    <t>BMO01_7_FB(+01).1_03</t>
+  </si>
+  <si>
+    <t>BMO01_8_FB(+01).1_04</t>
+  </si>
+  <si>
+    <t>BMO01_9_FB(+02).1_01</t>
   </si>
   <si>
     <t>Τύπος</t>
@@ -409,12 +409,6 @@
     <t>Aerial flat drop cable 2 FΟ</t>
   </si>
   <si>
-    <t>PILOT</t>
-  </si>
-  <si>
-    <t>ΤΖΩΝ ΚΕΝΝΕΝΤΥ 23</t>
-  </si>
-  <si>
     <t>12'= 4 μ cable</t>
   </si>
   <si>
@@ -502,21 +496,6 @@
     <t>COPY PASTE VALUES FROM ΤΑΒ ΟΡΟΦΟΙ</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>4"</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
     <t>5. ΣΤΟΙΧΕΙΑ ΚΑΜΠΙΝΑΣ/ LABEL BEP/BCP</t>
   </si>
   <si>
@@ -535,27 +514,15 @@
     <t>B</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
     <t>ΠΑΡΑΤΗΡΗΣΕΙΣ</t>
   </si>
   <si>
-    <t>από καμπίνα</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>SMALL BCP with 1 splitter  ZTT</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>ΑΓΙΟΥ ΚΩΝΣΤΑΝΤΙΝΟΥ 58</t>
-  </si>
-  <si>
     <t xml:space="preserve">6 ΟΡΙΖΟΝΤΟΓΡΑΦΙΑ. </t>
   </si>
   <si>
@@ -571,9 +538,6 @@
     <t>Μ/Σ</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>ΝΕΑ ΣΩΛΗΝΩΣΗ</t>
   </si>
   <si>
@@ -581,9 +545,6 @@
   </si>
   <si>
     <t>ΕΣΚΑΛΗΤ -BEP</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>ΕΣΚΑΛΗΤ Β1</t>
@@ -856,7 +817,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1149,21 +1110,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -1250,7 +1196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1364,34 +1310,51 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1405,10 +1368,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="9" fillId="6" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1419,14 +1382,14 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="9" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1436,7 +1399,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1496,16 +1459,13 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1552,54 +1512,25 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1610,7 +1541,77 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1756,76 +1757,6 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="lightUp"/>
       </fill>
     </dxf>
@@ -1852,187 +1783,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>203563</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2440,7 +2190,7 @@
         <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -2449,13 +2199,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
         <v>29</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>30</v>
-      </c>
-      <c r="K2" t="s">
-        <v>31</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
@@ -2467,34 +2217,34 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" t="s">
         <v>32</v>
       </c>
-      <c r="P2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" t="s">
-        <v>33</v>
-      </c>
       <c r="S2">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="T2">
-        <v>36.444828000000001</v>
+        <v>36.445973000000002</v>
       </c>
       <c r="U2">
-        <v>28.216799000000002</v>
+        <v>28.216908</v>
       </c>
       <c r="V2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="X2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2518,51 +2268,51 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -2574,39 +2324,39 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" t="s">
         <v>48</v>
       </c>
-      <c r="F2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" t="s">
-        <v>32</v>
-      </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -2618,39 +2368,39 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -2662,34 +2412,34 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L4" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="M4" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="N4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -2706,34 +2456,34 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2771,7 +2521,7 @@
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2782,7 +2532,7 @@
         <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2793,7 +2543,7 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2804,7 +2554,7 @@
         <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2815,7 +2565,7 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2826,7 +2576,7 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2837,7 +2587,7 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2848,7 +2598,7 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2859,7 +2609,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2870,7 +2620,7 @@
         <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2881,7 +2631,7 @@
         <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2892,7 +2642,7 @@
         <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2903,7 +2653,7 @@
         <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2914,7 +2664,7 @@
         <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -2925,7 +2675,7 @@
         <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -2936,7 +2686,7 @@
         <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2947,7 +2697,7 @@
         <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2958,7 +2708,7 @@
         <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2969,7 +2719,7 @@
         <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2980,7 +2730,7 @@
         <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2991,7 +2741,7 @@
         <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -3002,7 +2752,7 @@
         <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -3013,7 +2763,7 @@
         <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -3024,7 +2774,7 @@
         <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -3035,7 +2785,7 @@
         <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -3046,7 +2796,7 @@
         <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -3115,7 +2865,7 @@
         <v>92</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AC1" s="2" t="s">
         <v>93</v>
@@ -3157,25 +2907,25 @@
       </c>
     </row>
     <row r="3" spans="1:30" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="83" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
-      <c r="R3" s="79"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="84"/>
+      <c r="N3" s="84"/>
+      <c r="O3" s="84"/>
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
+      <c r="R3" s="85"/>
       <c r="U3" s="3" t="s">
         <v>105</v>
       </c>
@@ -3208,30 +2958,30 @@
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="86" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="81"/>
+      <c r="C4" s="87"/>
       <c r="D4" s="7" t="s">
         <v>115</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="F4" s="82" t="s">
+      <c r="F4" s="88" t="s">
         <v>117</v>
       </c>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="82"/>
-      <c r="O4" s="82"/>
-      <c r="P4" s="82"/>
-      <c r="Q4" s="82"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
       <c r="R4" s="8" t="s">
         <v>118</v>
       </c>
@@ -3261,73 +3011,63 @@
       </c>
     </row>
     <row r="5" spans="1:30" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="89"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="92"/>
+      <c r="K5" s="92"/>
+      <c r="L5" s="92"/>
+      <c r="M5" s="92"/>
+      <c r="N5" s="92"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="92"/>
+      <c r="Q5" s="93"/>
+      <c r="R5" s="11"/>
+      <c r="V5" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="84"/>
-      <c r="D5" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="85" t="s">
+      <c r="Y5" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="86"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="86"/>
-      <c r="N5" s="86"/>
-      <c r="O5" s="86"/>
-      <c r="P5" s="86"/>
-      <c r="Q5" s="87"/>
-      <c r="R5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="Y5" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="Z5" s="5"/>
       <c r="AB5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="83" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="84"/>
+      <c r="K6" s="84"/>
+      <c r="L6" s="84"/>
+      <c r="M6" s="84"/>
+      <c r="N6" s="84"/>
+      <c r="O6" s="84"/>
+      <c r="P6" s="84"/>
+      <c r="Q6" s="84"/>
+      <c r="R6" s="85"/>
+      <c r="V6" s="3" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="6" spans="1:30" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="77" t="s">
+      <c r="Y6" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="78"/>
-      <c r="L6" s="78"/>
-      <c r="M6" s="78"/>
-      <c r="N6" s="78"/>
-      <c r="O6" s="78"/>
-      <c r="P6" s="78"/>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="79"/>
-      <c r="V6" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y6" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="Z6" s="5"/>
       <c r="AB6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
@@ -3383,67 +3123,33 @@
         <v>17</v>
       </c>
       <c r="AB7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="16">
-        <v>4</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="P8" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q8" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="R8" s="17" t="s">
-        <v>33</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B8" s="15"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="17"/>
       <c r="V8" s="3"/>
       <c r="AB8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
@@ -3451,31 +3157,31 @@
       <c r="R9" s="19"/>
       <c r="V9" s="3"/>
       <c r="AB9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="94" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="95"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="95"/>
+      <c r="F10" s="95"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="95"/>
+      <c r="I10" s="95"/>
+      <c r="J10" s="95"/>
+      <c r="K10" s="95"/>
+      <c r="L10" s="95"/>
+      <c r="M10" s="95"/>
+      <c r="N10" s="95"/>
+      <c r="O10" s="95"/>
+      <c r="P10" s="95"/>
+      <c r="Q10" s="95"/>
+      <c r="R10" s="96"/>
+      <c r="AB10" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="88" t="s">
-        <v>139</v>
-      </c>
-      <c r="C10" s="89"/>
-      <c r="D10" s="89"/>
-      <c r="E10" s="89"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="89"/>
-      <c r="H10" s="89"/>
-      <c r="I10" s="89"/>
-      <c r="J10" s="89"/>
-      <c r="K10" s="89"/>
-      <c r="L10" s="89"/>
-      <c r="M10" s="89"/>
-      <c r="N10" s="89"/>
-      <c r="O10" s="89"/>
-      <c r="P10" s="89"/>
-      <c r="Q10" s="89"/>
-      <c r="R10" s="90"/>
-      <c r="AB10" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3497,7 +3203,7 @@
       <c r="Q11" s="21"/>
       <c r="R11" s="22"/>
       <c r="AB11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3510,7 +3216,7 @@
         <v>87</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G12" s="21"/>
       <c r="H12" s="24"/>
@@ -3525,21 +3231,15 @@
       <c r="Q12" s="21"/>
       <c r="R12" s="22"/>
       <c r="AB12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="20"/>
       <c r="C13" s="21"/>
-      <c r="D13" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="F13" s="9">
-        <v>211</v>
-      </c>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="9"/>
       <c r="G13" s="21"/>
       <c r="H13" s="24"/>
       <c r="I13" s="21"/>
@@ -3553,7 +3253,7 @@
       <c r="Q13" s="21"/>
       <c r="R13" s="22"/>
       <c r="AB13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3575,29 +3275,29 @@
       <c r="Q14" s="21"/>
       <c r="R14" s="22"/>
       <c r="AB14" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="88" t="s">
-        <v>146</v>
-      </c>
-      <c r="C15" s="89"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="89"/>
-      <c r="K15" s="89"/>
-      <c r="L15" s="89"/>
-      <c r="M15" s="89"/>
-      <c r="N15" s="89"/>
-      <c r="O15" s="89"/>
-      <c r="P15" s="89"/>
-      <c r="Q15" s="89"/>
-      <c r="R15" s="90"/>
+      <c r="B15" s="94" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="95"/>
+      <c r="K15" s="95"/>
+      <c r="L15" s="95"/>
+      <c r="M15" s="95"/>
+      <c r="N15" s="95"/>
+      <c r="O15" s="95"/>
+      <c r="P15" s="95"/>
+      <c r="Q15" s="95"/>
+      <c r="R15" s="96"/>
     </row>
     <row r="16" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="20"/>
@@ -3618,7 +3318,7 @@
       <c r="Q16" s="21"/>
       <c r="R16" s="22"/>
       <c r="AB16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3634,7 +3334,7 @@
         <v>93</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H17" s="21"/>
       <c r="I17" s="21"/>
@@ -3648,7 +3348,7 @@
       <c r="Q17" s="21"/>
       <c r="R17" s="22"/>
       <c r="AB17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3671,7 +3371,7 @@
       <c r="Q18" s="21"/>
       <c r="R18" s="22"/>
       <c r="AB18" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
@@ -3693,29 +3393,29 @@
       <c r="Q19" s="21"/>
       <c r="R19" s="22"/>
       <c r="AB19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="88" t="s">
-        <v>151</v>
-      </c>
-      <c r="C20" s="89"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="89"/>
-      <c r="K20" s="89"/>
-      <c r="L20" s="89"/>
-      <c r="M20" s="89"/>
-      <c r="N20" s="89"/>
-      <c r="O20" s="89"/>
-      <c r="P20" s="89"/>
-      <c r="Q20" s="89"/>
-      <c r="R20" s="90"/>
+      <c r="B20" s="94" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" s="95"/>
+      <c r="D20" s="95"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="95"/>
+      <c r="I20" s="95"/>
+      <c r="J20" s="95"/>
+      <c r="K20" s="95"/>
+      <c r="L20" s="95"/>
+      <c r="M20" s="95"/>
+      <c r="N20" s="95"/>
+      <c r="O20" s="95"/>
+      <c r="P20" s="95"/>
+      <c r="Q20" s="95"/>
+      <c r="R20" s="96"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B21" s="29"/>
@@ -3738,13 +3438,11 @@
     </row>
     <row r="22" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>134</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C22" s="25"/>
       <c r="D22" s="25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E22" s="21"/>
       <c r="F22" s="21"/>
@@ -3782,267 +3480,155 @@
     </row>
     <row r="24" spans="1:28" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="D24" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="36" t="s">
+      <c r="E24" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="36" t="s">
+      <c r="F24" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="F24" s="36" t="s">
+      <c r="G24" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="G24" s="36" t="s">
+      <c r="H24" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="36" t="s">
-        <v>40</v>
-      </c>
       <c r="I24" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="K24" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="L24" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="M24" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="N24" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="J24" s="36" t="s">
+      <c r="O24" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="P24" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q24" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="K24" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="L24" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="M24" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="N24" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="O24" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="P24" s="37" t="s">
+      <c r="R24" s="22"/>
+    </row>
+    <row r="25" spans="1:28" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="97" t="s">
         <v>154</v>
       </c>
-      <c r="Q24" s="38" t="s">
-        <v>155</v>
-      </c>
-      <c r="R24" s="22"/>
-    </row>
-    <row r="25" spans="1:28" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="91" t="s">
-        <v>156</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="16">
-        <v>2</v>
-      </c>
-      <c r="D25" s="16">
-        <v>0</v>
-      </c>
-      <c r="E25" s="16">
-        <v>2</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G25" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="J25" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K25" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="L25" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="M25" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="N25" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="O25" s="36" t="s">
-        <v>32</v>
-      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="36"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="36"/>
       <c r="P25" s="9" t="s">
-        <v>157</v>
+        <v>31</v>
       </c>
       <c r="Q25" s="11" t="s">
-        <v>158</v>
+        <v>31</v>
       </c>
       <c r="R25" s="22"/>
     </row>
     <row r="26" spans="1:28" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="91"/>
-      <c r="B26" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="16">
-        <v>2</v>
-      </c>
-      <c r="D26" s="16">
-        <v>0</v>
-      </c>
-      <c r="E26" s="16">
-        <v>2</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G26" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="J26" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K26" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="L26" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="M26" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="N26" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="O26" s="36" t="s">
-        <v>32</v>
-      </c>
+      <c r="A26" s="97"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="36"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="36"/>
       <c r="P26" s="9" t="s">
-        <v>159</v>
+        <v>31</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>158</v>
+        <v>31</v>
       </c>
       <c r="R26" s="22"/>
     </row>
     <row r="27" spans="1:28" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="91"/>
-      <c r="B27" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="16">
-        <v>2</v>
-      </c>
-      <c r="D27" s="16">
-        <v>0</v>
-      </c>
-      <c r="E27" s="16">
-        <v>2</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="J27" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K27" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="L27" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="M27" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="N27" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="O27" s="36" t="s">
-        <v>32</v>
-      </c>
+      <c r="A27" s="97"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="36"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="36"/>
       <c r="P27" s="9" t="s">
-        <v>160</v>
+        <v>31</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>158</v>
+        <v>31</v>
       </c>
       <c r="R27" s="22"/>
     </row>
     <row r="28" spans="1:28" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="91"/>
-      <c r="B28" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="16">
-        <v>1</v>
-      </c>
-      <c r="D28" s="16">
-        <v>0</v>
-      </c>
-      <c r="E28" s="16">
-        <v>1</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G28" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="H28" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="J28" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="L28" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="M28" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="N28" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="O28" s="36" t="s">
-        <v>32</v>
-      </c>
+      <c r="A28" s="97"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="36"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="36"/>
       <c r="P28" s="9" t="s">
-        <v>161</v>
+        <v>31</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>158</v>
+        <v>31</v>
       </c>
       <c r="R28" s="22"/>
     </row>
     <row r="29" spans="1:28" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="91"/>
+      <c r="A29" s="97"/>
       <c r="B29" s="15"/>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -4062,7 +3648,7 @@
       <c r="R29" s="22"/>
     </row>
     <row r="30" spans="1:28" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="91"/>
+      <c r="A30" s="97"/>
       <c r="B30" s="15"/>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
@@ -4082,7 +3668,7 @@
       <c r="R30" s="22"/>
     </row>
     <row r="31" spans="1:28" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="91"/>
+      <c r="A31" s="97"/>
       <c r="B31" s="15"/>
       <c r="C31" s="16"/>
       <c r="D31" s="16"/>
@@ -4102,7 +3688,7 @@
       <c r="R31" s="22"/>
     </row>
     <row r="32" spans="1:28" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="91"/>
+      <c r="A32" s="97"/>
       <c r="B32" s="15"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
@@ -4122,7 +3708,7 @@
       <c r="R32" s="22"/>
     </row>
     <row r="33" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="91"/>
+      <c r="A33" s="97"/>
       <c r="B33" s="15"/>
       <c r="C33" s="16"/>
       <c r="D33" s="16"/>
@@ -4142,7 +3728,7 @@
       <c r="R33" s="22"/>
     </row>
     <row r="34" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="91"/>
+      <c r="A34" s="97"/>
       <c r="B34" s="15"/>
       <c r="C34" s="16"/>
       <c r="D34" s="16"/>
@@ -4162,7 +3748,7 @@
       <c r="R34" s="22"/>
     </row>
     <row r="35" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="91"/>
+      <c r="A35" s="97"/>
       <c r="B35" s="15"/>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
@@ -4182,7 +3768,7 @@
       <c r="R35" s="22"/>
     </row>
     <row r="36" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="91"/>
+      <c r="A36" s="97"/>
       <c r="B36" s="15"/>
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
@@ -4202,7 +3788,7 @@
       <c r="R36" s="22"/>
     </row>
     <row r="37" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="91"/>
+      <c r="A37" s="97"/>
       <c r="B37" s="15"/>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
@@ -4222,7 +3808,7 @@
       <c r="R37" s="22"/>
     </row>
     <row r="38" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="91"/>
+      <c r="A38" s="97"/>
       <c r="B38" s="15"/>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
@@ -4242,7 +3828,7 @@
       <c r="R38" s="22"/>
     </row>
     <row r="39" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="91"/>
+      <c r="A39" s="97"/>
       <c r="B39" s="15"/>
       <c r="C39" s="16"/>
       <c r="D39" s="16"/>
@@ -4300,48 +3886,44 @@
       <c r="R41" s="41"/>
     </row>
     <row r="42" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="88" t="s">
-        <v>162</v>
-      </c>
-      <c r="C42" s="89"/>
-      <c r="D42" s="89"/>
-      <c r="E42" s="89"/>
-      <c r="F42" s="89"/>
-      <c r="G42" s="89"/>
-      <c r="H42" s="89"/>
-      <c r="I42" s="89"/>
-      <c r="J42" s="89"/>
-      <c r="K42" s="89"/>
-      <c r="L42" s="89"/>
-      <c r="M42" s="89"/>
-      <c r="N42" s="89"/>
-      <c r="O42" s="89"/>
-      <c r="P42" s="89"/>
-      <c r="Q42" s="89"/>
-      <c r="R42" s="90"/>
-      <c r="S42" s="77" t="s">
-        <v>163</v>
-      </c>
-      <c r="T42" s="78"/>
-      <c r="U42" s="78"/>
-      <c r="V42" s="78"/>
-      <c r="W42" s="78"/>
-      <c r="X42" s="78"/>
-      <c r="Y42" s="78"/>
-      <c r="Z42" s="78"/>
-      <c r="AA42" s="79"/>
+      <c r="B42" s="94" t="s">
+        <v>155</v>
+      </c>
+      <c r="C42" s="95"/>
+      <c r="D42" s="95"/>
+      <c r="E42" s="95"/>
+      <c r="F42" s="95"/>
+      <c r="G42" s="95"/>
+      <c r="H42" s="95"/>
+      <c r="I42" s="95"/>
+      <c r="J42" s="95"/>
+      <c r="K42" s="95"/>
+      <c r="L42" s="95"/>
+      <c r="M42" s="95"/>
+      <c r="N42" s="95"/>
+      <c r="O42" s="95"/>
+      <c r="P42" s="95"/>
+      <c r="Q42" s="95"/>
+      <c r="R42" s="96"/>
+      <c r="S42" s="83" t="s">
+        <v>156</v>
+      </c>
+      <c r="T42" s="84"/>
+      <c r="U42" s="84"/>
+      <c r="V42" s="84"/>
+      <c r="W42" s="84"/>
+      <c r="X42" s="84"/>
+      <c r="Y42" s="84"/>
+      <c r="Z42" s="84"/>
+      <c r="AA42" s="85"/>
     </row>
     <row r="43" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="42"/>
       <c r="C43" s="43"/>
       <c r="D43" s="43"/>
       <c r="E43" s="43"/>
-      <c r="F43" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="G43" s="44" t="s">
-        <v>54</v>
-      </c>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
       <c r="H43" s="43"/>
       <c r="I43" s="43"/>
       <c r="J43" s="43"/>
@@ -4364,19 +3946,14 @@
       <c r="AA43" s="45"/>
     </row>
     <row r="44" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="92" t="s">
-        <v>164</v>
+      <c r="A44" s="98" t="s">
+        <v>157</v>
       </c>
       <c r="B44" s="42"/>
       <c r="C44" s="43"/>
       <c r="D44" s="43"/>
       <c r="E44" s="21"/>
-      <c r="F44" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="G44" t="s">
-        <v>60</v>
-      </c>
+      <c r="F44" s="46"/>
       <c r="H44" s="43"/>
       <c r="I44" s="43"/>
       <c r="J44" s="43"/>
@@ -4399,17 +3976,12 @@
       <c r="AA44" s="45"/>
     </row>
     <row r="45" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="92"/>
+      <c r="A45" s="98"/>
       <c r="B45" s="42"/>
       <c r="C45" s="43"/>
       <c r="D45" s="43"/>
       <c r="E45" s="21"/>
-      <c r="F45" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="G45" t="s">
-        <v>57</v>
-      </c>
+      <c r="F45" s="46"/>
       <c r="H45" s="43"/>
       <c r="I45" s="43"/>
       <c r="J45" s="43"/>
@@ -4420,29 +3992,24 @@
       <c r="O45" s="43"/>
       <c r="P45" s="43"/>
       <c r="Q45" s="43"/>
-      <c r="R45" s="111"/>
-      <c r="S45" s="111"/>
-      <c r="T45" s="111"/>
-      <c r="U45" s="111"/>
-      <c r="V45" s="111"/>
-      <c r="W45" s="111"/>
-      <c r="X45" s="111"/>
-      <c r="Y45" s="111"/>
+      <c r="R45" s="43"/>
+      <c r="S45" s="43"/>
+      <c r="T45" s="43"/>
+      <c r="U45" s="43"/>
+      <c r="V45" s="43"/>
+      <c r="W45" s="43"/>
+      <c r="X45" s="43"/>
+      <c r="Y45" s="43"/>
       <c r="Z45" s="43"/>
       <c r="AA45" s="45"/>
     </row>
     <row r="46" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="92"/>
+      <c r="A46" s="98"/>
       <c r="B46" s="42"/>
       <c r="C46" s="43"/>
       <c r="D46" s="43"/>
       <c r="E46" s="21"/>
-      <c r="F46" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="G46" t="s">
-        <v>58</v>
-      </c>
+      <c r="F46" s="46"/>
       <c r="H46" s="43"/>
       <c r="I46" s="43"/>
       <c r="J46" s="43"/>
@@ -4453,29 +4020,24 @@
       <c r="O46" s="43"/>
       <c r="P46" s="43"/>
       <c r="Q46" s="43"/>
-      <c r="R46" s="111"/>
-      <c r="S46" s="111"/>
-      <c r="T46" s="119"/>
-      <c r="U46" s="119"/>
-      <c r="V46" s="120"/>
-      <c r="W46" s="120"/>
-      <c r="X46" s="120"/>
-      <c r="Y46" s="111"/>
+      <c r="R46" s="43"/>
+      <c r="S46" s="43"/>
+      <c r="T46" s="99"/>
+      <c r="U46" s="99"/>
+      <c r="V46" s="47"/>
+      <c r="W46" s="47"/>
+      <c r="X46" s="47"/>
+      <c r="Y46" s="43"/>
       <c r="Z46" s="43"/>
       <c r="AA46" s="45"/>
     </row>
     <row r="47" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="92"/>
+      <c r="A47" s="98"/>
       <c r="B47" s="42"/>
       <c r="C47" s="43"/>
       <c r="D47" s="43"/>
       <c r="E47" s="21"/>
-      <c r="F47" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="G47" t="s">
-        <v>59</v>
-      </c>
+      <c r="F47" s="46"/>
       <c r="H47" s="43"/>
       <c r="I47" s="43"/>
       <c r="J47" s="43"/>
@@ -4486,19 +4048,19 @@
       <c r="O47" s="43"/>
       <c r="P47" s="43"/>
       <c r="Q47" s="43"/>
-      <c r="R47" s="111"/>
-      <c r="S47" s="111"/>
-      <c r="T47" s="112"/>
-      <c r="U47" s="113"/>
-      <c r="V47" s="112"/>
-      <c r="W47" s="113"/>
-      <c r="X47" s="113"/>
-      <c r="Y47" s="111"/>
+      <c r="R47" s="43"/>
+      <c r="S47" s="43"/>
+      <c r="T47" s="48"/>
+      <c r="U47" s="49"/>
+      <c r="V47" s="48"/>
+      <c r="W47" s="49"/>
+      <c r="X47" s="49"/>
+      <c r="Y47" s="43"/>
       <c r="Z47" s="43"/>
       <c r="AA47" s="45"/>
     </row>
     <row r="48" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="92"/>
+      <c r="A48" s="98"/>
       <c r="B48" s="42"/>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
@@ -4515,37 +4077,37 @@
       <c r="O48" s="21"/>
       <c r="P48" s="21"/>
       <c r="Q48" s="21"/>
-      <c r="R48" s="125"/>
-      <c r="S48" s="111"/>
-      <c r="T48" s="113"/>
-      <c r="U48" s="112"/>
-      <c r="V48" s="113"/>
-      <c r="W48" s="121"/>
-      <c r="X48" s="114"/>
-      <c r="Y48" s="111"/>
+      <c r="R48" s="21"/>
+      <c r="S48" s="43"/>
+      <c r="T48" s="49"/>
+      <c r="U48" s="48"/>
+      <c r="V48" s="49"/>
+      <c r="W48" s="50"/>
+      <c r="X48" s="51"/>
+      <c r="Y48" s="43"/>
       <c r="Z48" s="43"/>
       <c r="AA48" s="45"/>
     </row>
     <row r="49" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="92"/>
+      <c r="A49" s="98"/>
       <c r="B49" s="42"/>
       <c r="C49" s="43" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D49" s="43" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E49" s="43" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="F49" s="43" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="G49" s="43" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H49" s="43" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="I49" s="43"/>
       <c r="J49" s="43"/>
@@ -4556,31 +4118,29 @@
       <c r="O49" s="43"/>
       <c r="P49" s="43"/>
       <c r="Q49" s="43"/>
-      <c r="R49" s="111"/>
-      <c r="S49" s="111"/>
-      <c r="T49" s="113"/>
-      <c r="U49" s="112"/>
-      <c r="V49" s="113"/>
-      <c r="W49" s="112"/>
-      <c r="X49" s="115"/>
-      <c r="Y49" s="111"/>
+      <c r="R49" s="43"/>
+      <c r="S49" s="43"/>
+      <c r="T49" s="49"/>
+      <c r="U49" s="48"/>
+      <c r="V49" s="49"/>
+      <c r="W49" s="48"/>
+      <c r="X49" s="52"/>
+      <c r="Y49" s="43"/>
       <c r="Z49" s="43"/>
       <c r="AA49" s="45"/>
     </row>
-    <row r="50" spans="1:27" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="92"/>
+    <row r="50" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="98"/>
       <c r="B50" s="42"/>
       <c r="C50" s="43">
         <v>1</v>
       </c>
       <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="43" t="s">
-        <v>169</v>
-      </c>
-      <c r="I50" s="43"/>
+      <c r="E50" s="116"/>
+      <c r="F50" s="116"/>
+      <c r="G50" s="116"/>
+      <c r="H50" s="116"/>
+      <c r="I50" s="116"/>
       <c r="J50" s="43"/>
       <c r="K50" s="43"/>
       <c r="L50" s="43"/>
@@ -4589,19 +4149,19 @@
       <c r="O50" s="43"/>
       <c r="P50" s="43"/>
       <c r="Q50" s="43"/>
-      <c r="R50" s="111"/>
-      <c r="S50" s="111"/>
-      <c r="T50" s="113"/>
-      <c r="U50" s="116"/>
-      <c r="V50" s="113"/>
-      <c r="W50" s="116"/>
-      <c r="X50" s="115"/>
-      <c r="Y50" s="111"/>
+      <c r="R50" s="43"/>
+      <c r="S50" s="43"/>
+      <c r="T50" s="49"/>
+      <c r="U50" s="53"/>
+      <c r="V50" s="49"/>
+      <c r="W50" s="53"/>
+      <c r="X50" s="52"/>
+      <c r="Y50" s="43"/>
       <c r="Z50" s="43"/>
       <c r="AA50" s="45"/>
     </row>
-    <row r="51" spans="1:27" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="92"/>
+    <row r="51" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="98"/>
       <c r="B51" s="42"/>
       <c r="C51" s="43">
         <v>2</v>
@@ -4610,16 +4170,11 @@
         <f>AB47</f>
         <v>0</v>
       </c>
-      <c r="E51" s="43">
-        <f>AB48</f>
-        <v>0</v>
-      </c>
-      <c r="F51" s="93" t="s">
-        <v>172</v>
-      </c>
-      <c r="G51" s="94"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="43"/>
+      <c r="E51" s="116"/>
+      <c r="F51" s="117"/>
+      <c r="G51" s="117"/>
+      <c r="H51" s="118"/>
+      <c r="I51" s="116"/>
       <c r="J51" s="43"/>
       <c r="K51" s="43"/>
       <c r="L51" s="43"/>
@@ -4628,14 +4183,14 @@
       <c r="O51" s="43"/>
       <c r="P51" s="43"/>
       <c r="Q51" s="43"/>
-      <c r="R51" s="111"/>
-      <c r="S51" s="111"/>
-      <c r="T51" s="113"/>
-      <c r="U51" s="116"/>
-      <c r="V51" s="113"/>
-      <c r="W51" s="116"/>
-      <c r="X51" s="115"/>
-      <c r="Y51" s="111"/>
+      <c r="R51" s="43"/>
+      <c r="S51" s="43"/>
+      <c r="T51" s="49"/>
+      <c r="U51" s="53"/>
+      <c r="V51" s="49"/>
+      <c r="W51" s="53"/>
+      <c r="X51" s="52"/>
+      <c r="Y51" s="43"/>
       <c r="Z51" s="43"/>
       <c r="AA51" s="45"/>
     </row>
@@ -4648,20 +4203,11 @@
         <f>AB51</f>
         <v>0</v>
       </c>
-      <c r="E52" s="43">
-        <f>AB52</f>
-        <v>0</v>
-      </c>
-      <c r="F52" s="51" t="s">
-        <v>165</v>
-      </c>
-      <c r="G52" s="47" t="s">
-        <v>173</v>
-      </c>
-      <c r="H52" s="48" t="s">
-        <v>168</v>
-      </c>
-      <c r="I52" s="43"/>
+      <c r="E52" s="116"/>
+      <c r="F52" s="119"/>
+      <c r="G52" s="120"/>
+      <c r="H52" s="120"/>
+      <c r="I52" s="116"/>
       <c r="J52" s="43"/>
       <c r="K52" s="43"/>
       <c r="L52" s="43"/>
@@ -4670,14 +4216,14 @@
       <c r="O52" s="43"/>
       <c r="P52" s="43"/>
       <c r="Q52" s="43"/>
-      <c r="R52" s="111"/>
-      <c r="S52" s="111"/>
-      <c r="T52" s="113"/>
-      <c r="U52" s="116"/>
-      <c r="V52" s="113"/>
-      <c r="W52" s="116"/>
-      <c r="X52" s="115"/>
-      <c r="Y52" s="111"/>
+      <c r="R52" s="43"/>
+      <c r="S52" s="43"/>
+      <c r="T52" s="49"/>
+      <c r="U52" s="53"/>
+      <c r="V52" s="49"/>
+      <c r="W52" s="53"/>
+      <c r="X52" s="52"/>
+      <c r="Y52" s="43"/>
       <c r="Z52" s="43"/>
       <c r="AA52" s="45"/>
     </row>
@@ -4690,20 +4236,11 @@
         <f>AB55</f>
         <v>0</v>
       </c>
-      <c r="E53" s="43">
-        <f>AB56</f>
-        <v>0</v>
-      </c>
-      <c r="F53" s="49">
-        <v>1</v>
-      </c>
-      <c r="G53" s="50">
-        <v>249</v>
-      </c>
-      <c r="H53" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="I53" s="43"/>
+      <c r="E53" s="116"/>
+      <c r="F53" s="120"/>
+      <c r="G53" s="121"/>
+      <c r="H53" s="122"/>
+      <c r="I53" s="116"/>
       <c r="J53" s="43"/>
       <c r="K53" s="43"/>
       <c r="L53" s="43"/>
@@ -4712,14 +4249,14 @@
       <c r="O53" s="43"/>
       <c r="P53" s="43"/>
       <c r="Q53" s="43"/>
-      <c r="R53" s="111"/>
-      <c r="S53" s="111"/>
-      <c r="T53" s="113"/>
-      <c r="U53" s="116"/>
-      <c r="V53" s="113"/>
-      <c r="W53" s="116"/>
-      <c r="X53" s="115"/>
-      <c r="Y53" s="111"/>
+      <c r="R53" s="43"/>
+      <c r="S53" s="43"/>
+      <c r="T53" s="49"/>
+      <c r="U53" s="53"/>
+      <c r="V53" s="49"/>
+      <c r="W53" s="53"/>
+      <c r="X53" s="52"/>
+      <c r="Y53" s="43"/>
       <c r="Z53" s="43"/>
       <c r="AA53" s="45"/>
     </row>
@@ -4732,20 +4269,11 @@
         <f>AB59</f>
         <v>0</v>
       </c>
-      <c r="E54" s="43">
-        <f>AB60</f>
-        <v>0</v>
-      </c>
-      <c r="F54" s="49">
-        <v>2</v>
-      </c>
-      <c r="G54" s="50">
-        <v>250</v>
-      </c>
-      <c r="H54" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="I54" s="43"/>
+      <c r="E54" s="116"/>
+      <c r="F54" s="120"/>
+      <c r="G54" s="121"/>
+      <c r="H54" s="122"/>
+      <c r="I54" s="116"/>
       <c r="J54" s="43"/>
       <c r="K54" s="43"/>
       <c r="L54" s="43"/>
@@ -4754,14 +4282,14 @@
       <c r="O54" s="43"/>
       <c r="P54" s="43"/>
       <c r="Q54" s="43"/>
-      <c r="R54" s="111"/>
-      <c r="S54" s="111"/>
-      <c r="T54" s="113"/>
-      <c r="U54" s="116"/>
-      <c r="V54" s="113"/>
-      <c r="W54" s="116"/>
-      <c r="X54" s="115"/>
-      <c r="Y54" s="111"/>
+      <c r="R54" s="43"/>
+      <c r="S54" s="43"/>
+      <c r="T54" s="49"/>
+      <c r="U54" s="53"/>
+      <c r="V54" s="49"/>
+      <c r="W54" s="53"/>
+      <c r="X54" s="52"/>
+      <c r="Y54" s="43"/>
       <c r="Z54" s="43"/>
       <c r="AA54" s="45"/>
     </row>
@@ -4774,20 +4302,11 @@
         <f>AB63</f>
         <v>0</v>
       </c>
-      <c r="E55" s="43">
-        <f>AB64</f>
-        <v>0</v>
-      </c>
-      <c r="F55" s="49">
-        <v>3</v>
-      </c>
-      <c r="G55" s="50">
-        <v>251</v>
-      </c>
-      <c r="H55" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="I55" s="43"/>
+      <c r="E55" s="116"/>
+      <c r="F55" s="120"/>
+      <c r="G55" s="121"/>
+      <c r="H55" s="122"/>
+      <c r="I55" s="116"/>
       <c r="J55" s="43"/>
       <c r="K55" s="43"/>
       <c r="L55" s="43"/>
@@ -4796,18 +4315,18 @@
       <c r="O55" s="43"/>
       <c r="P55" s="43"/>
       <c r="Q55" s="43"/>
-      <c r="R55" s="111"/>
-      <c r="S55" s="111"/>
-      <c r="T55" s="113"/>
-      <c r="U55" s="116"/>
-      <c r="V55" s="113"/>
-      <c r="W55" s="116"/>
-      <c r="X55" s="115"/>
-      <c r="Y55" s="111"/>
+      <c r="R55" s="43"/>
+      <c r="S55" s="43"/>
+      <c r="T55" s="49"/>
+      <c r="U55" s="53"/>
+      <c r="V55" s="49"/>
+      <c r="W55" s="53"/>
+      <c r="X55" s="52"/>
+      <c r="Y55" s="43"/>
       <c r="Z55" s="43"/>
       <c r="AA55" s="45"/>
     </row>
-    <row r="56" spans="1:27" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="42"/>
       <c r="C56" s="43">
         <v>7</v>
@@ -4816,20 +4335,11 @@
         <f>AB67</f>
         <v>0</v>
       </c>
-      <c r="E56" s="43">
-        <f>AB68</f>
-        <v>0</v>
-      </c>
-      <c r="F56" s="53">
-        <v>4</v>
-      </c>
-      <c r="G56" s="50">
-        <v>252</v>
-      </c>
-      <c r="H56" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="I56" s="43"/>
+      <c r="E56" s="116"/>
+      <c r="F56" s="120"/>
+      <c r="G56" s="121"/>
+      <c r="H56" s="122"/>
+      <c r="I56" s="116"/>
       <c r="J56" s="43"/>
       <c r="K56" s="43"/>
       <c r="L56" s="43"/>
@@ -4838,14 +4348,14 @@
       <c r="O56" s="43"/>
       <c r="P56" s="43"/>
       <c r="Q56" s="43"/>
-      <c r="R56" s="111"/>
-      <c r="S56" s="111"/>
-      <c r="T56" s="113"/>
-      <c r="U56" s="116"/>
-      <c r="V56" s="113"/>
-      <c r="W56" s="116"/>
-      <c r="X56" s="115"/>
-      <c r="Y56" s="111"/>
+      <c r="R56" s="43"/>
+      <c r="S56" s="43"/>
+      <c r="T56" s="49"/>
+      <c r="U56" s="53"/>
+      <c r="V56" s="49"/>
+      <c r="W56" s="53"/>
+      <c r="X56" s="52"/>
+      <c r="Y56" s="43"/>
       <c r="Z56" s="43"/>
       <c r="AA56" s="45"/>
     </row>
@@ -4858,20 +4368,11 @@
         <f>AB71</f>
         <v>0</v>
       </c>
-      <c r="E57" s="43">
-        <f>AB72</f>
-        <v>0</v>
-      </c>
-      <c r="F57" s="43">
-        <f>AB73</f>
-        <v>0</v>
-      </c>
-      <c r="G57" s="43">
-        <f>AB74</f>
-        <v>0</v>
-      </c>
-      <c r="H57" s="43"/>
-      <c r="I57" s="43"/>
+      <c r="E57" s="116"/>
+      <c r="F57" s="116"/>
+      <c r="G57" s="116"/>
+      <c r="H57" s="116"/>
+      <c r="I57" s="116"/>
       <c r="J57" s="43"/>
       <c r="K57" s="43"/>
       <c r="L57" s="43"/>
@@ -4880,14 +4381,14 @@
       <c r="O57" s="43"/>
       <c r="P57" s="43"/>
       <c r="Q57" s="43"/>
-      <c r="R57" s="111"/>
-      <c r="S57" s="111"/>
-      <c r="T57" s="113"/>
-      <c r="U57" s="116"/>
-      <c r="V57" s="113"/>
-      <c r="W57" s="116"/>
-      <c r="X57" s="115"/>
-      <c r="Y57" s="111"/>
+      <c r="R57" s="43"/>
+      <c r="S57" s="43"/>
+      <c r="T57" s="49"/>
+      <c r="U57" s="53"/>
+      <c r="V57" s="49"/>
+      <c r="W57" s="53"/>
+      <c r="X57" s="52"/>
+      <c r="Y57" s="43"/>
       <c r="Z57" s="43"/>
       <c r="AA57" s="45"/>
     </row>
@@ -4900,20 +4401,11 @@
         <f>AB75</f>
         <v>0</v>
       </c>
-      <c r="E58" s="43">
-        <f>AB76</f>
-        <v>0</v>
-      </c>
-      <c r="F58" s="43">
-        <f>AB77</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="43">
-        <f>AB78</f>
-        <v>0</v>
-      </c>
-      <c r="H58" s="43"/>
-      <c r="I58" s="43"/>
+      <c r="E58" s="116"/>
+      <c r="F58" s="116"/>
+      <c r="G58" s="116"/>
+      <c r="H58" s="116"/>
+      <c r="I58" s="116"/>
       <c r="J58" s="43"/>
       <c r="K58" s="43"/>
       <c r="L58" s="43"/>
@@ -4922,14 +4414,14 @@
       <c r="O58" s="43"/>
       <c r="P58" s="43"/>
       <c r="Q58" s="43"/>
-      <c r="R58" s="111"/>
-      <c r="S58" s="111"/>
-      <c r="T58" s="113"/>
-      <c r="U58" s="116"/>
-      <c r="V58" s="113"/>
-      <c r="W58" s="116"/>
-      <c r="X58" s="115"/>
-      <c r="Y58" s="111"/>
+      <c r="R58" s="43"/>
+      <c r="S58" s="43"/>
+      <c r="T58" s="49"/>
+      <c r="U58" s="53"/>
+      <c r="V58" s="49"/>
+      <c r="W58" s="53"/>
+      <c r="X58" s="52"/>
+      <c r="Y58" s="43"/>
       <c r="Z58" s="43"/>
       <c r="AA58" s="45"/>
     </row>
@@ -4950,14 +4442,14 @@
       <c r="O59" s="43"/>
       <c r="P59" s="43"/>
       <c r="Q59" s="43"/>
-      <c r="R59" s="111"/>
-      <c r="S59" s="111"/>
-      <c r="T59" s="113"/>
-      <c r="U59" s="116"/>
-      <c r="V59" s="113"/>
-      <c r="W59" s="116"/>
-      <c r="X59" s="115"/>
-      <c r="Y59" s="111"/>
+      <c r="R59" s="43"/>
+      <c r="S59" s="43"/>
+      <c r="T59" s="49"/>
+      <c r="U59" s="53"/>
+      <c r="V59" s="49"/>
+      <c r="W59" s="53"/>
+      <c r="X59" s="52"/>
+      <c r="Y59" s="43"/>
       <c r="Z59" s="43"/>
       <c r="AA59" s="45"/>
     </row>
@@ -4978,350 +4470,350 @@
       <c r="O60" s="43"/>
       <c r="P60" s="43"/>
       <c r="Q60" s="43"/>
-      <c r="R60" s="111"/>
-      <c r="S60" s="111"/>
-      <c r="T60" s="117"/>
-      <c r="U60" s="116"/>
-      <c r="V60" s="113"/>
-      <c r="W60" s="116"/>
-      <c r="X60" s="118"/>
-      <c r="Y60" s="111"/>
+      <c r="R60" s="43"/>
+      <c r="S60" s="43"/>
+      <c r="T60" s="54"/>
+      <c r="U60" s="53"/>
+      <c r="V60" s="49"/>
+      <c r="W60" s="53"/>
+      <c r="X60" s="55"/>
+      <c r="Y60" s="43"/>
       <c r="Z60" s="43"/>
       <c r="AA60" s="45"/>
     </row>
     <row r="61" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="42"/>
-      <c r="C61" s="111"/>
-      <c r="D61" s="111"/>
-      <c r="E61" s="111"/>
-      <c r="F61" s="119"/>
-      <c r="G61" s="119"/>
-      <c r="H61" s="120"/>
-      <c r="I61" s="120"/>
-      <c r="J61" s="120"/>
-      <c r="K61" s="111"/>
-      <c r="L61" s="111"/>
-      <c r="M61" s="111"/>
+      <c r="C61" s="43"/>
+      <c r="D61" s="43"/>
+      <c r="E61" s="43"/>
+      <c r="F61" s="99"/>
+      <c r="G61" s="99"/>
+      <c r="H61" s="47"/>
+      <c r="I61" s="47"/>
+      <c r="J61" s="47"/>
+      <c r="K61" s="43"/>
+      <c r="L61" s="43"/>
+      <c r="M61" s="43"/>
       <c r="N61" s="43"/>
       <c r="O61" s="43"/>
       <c r="P61" s="43"/>
       <c r="Q61" s="43"/>
-      <c r="R61" s="111"/>
-      <c r="S61" s="111"/>
-      <c r="T61" s="117"/>
-      <c r="U61" s="116"/>
-      <c r="V61" s="113"/>
-      <c r="W61" s="116"/>
-      <c r="X61" s="118"/>
-      <c r="Y61" s="111"/>
+      <c r="R61" s="43"/>
+      <c r="S61" s="43"/>
+      <c r="T61" s="54"/>
+      <c r="U61" s="53"/>
+      <c r="V61" s="49"/>
+      <c r="W61" s="53"/>
+      <c r="X61" s="55"/>
+      <c r="Y61" s="43"/>
       <c r="Z61" s="43"/>
       <c r="AA61" s="45"/>
     </row>
     <row r="62" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="42"/>
-      <c r="C62" s="111"/>
-      <c r="D62" s="111"/>
-      <c r="E62" s="111"/>
-      <c r="F62" s="112"/>
-      <c r="G62" s="113"/>
-      <c r="H62" s="112"/>
-      <c r="I62" s="113"/>
-      <c r="J62" s="123"/>
-      <c r="K62" s="111"/>
-      <c r="L62" s="113"/>
-      <c r="M62" s="111"/>
+      <c r="C62" s="43"/>
+      <c r="D62" s="43"/>
+      <c r="E62" s="43"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="49"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="49"/>
+      <c r="J62" s="56"/>
+      <c r="K62" s="43"/>
+      <c r="L62" s="49"/>
+      <c r="M62" s="43"/>
       <c r="N62" s="43"/>
       <c r="O62" s="43"/>
       <c r="P62" s="43"/>
       <c r="Q62" s="43"/>
-      <c r="R62" s="111"/>
-      <c r="S62" s="111"/>
-      <c r="T62" s="117"/>
-      <c r="U62" s="116"/>
-      <c r="V62" s="113"/>
-      <c r="W62" s="116"/>
-      <c r="X62" s="118"/>
-      <c r="Y62" s="111"/>
+      <c r="R62" s="43"/>
+      <c r="S62" s="43"/>
+      <c r="T62" s="54"/>
+      <c r="U62" s="53"/>
+      <c r="V62" s="49"/>
+      <c r="W62" s="53"/>
+      <c r="X62" s="55"/>
+      <c r="Y62" s="43"/>
       <c r="Z62" s="43"/>
       <c r="AA62" s="45"/>
     </row>
     <row r="63" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="42"/>
-      <c r="C63" s="111"/>
-      <c r="D63" s="111"/>
-      <c r="E63" s="111"/>
-      <c r="F63" s="113"/>
-      <c r="G63" s="112"/>
-      <c r="H63" s="113"/>
-      <c r="I63" s="121"/>
-      <c r="J63" s="114"/>
-      <c r="K63" s="111"/>
-      <c r="L63" s="111"/>
-      <c r="M63" s="111"/>
+      <c r="C63" s="43"/>
+      <c r="D63" s="43"/>
+      <c r="E63" s="43"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="48"/>
+      <c r="H63" s="49"/>
+      <c r="I63" s="50"/>
+      <c r="J63" s="51"/>
+      <c r="K63" s="43"/>
+      <c r="L63" s="43"/>
+      <c r="M63" s="43"/>
       <c r="N63" s="43"/>
       <c r="O63" s="43"/>
       <c r="P63" s="43"/>
       <c r="Q63" s="43"/>
-      <c r="R63" s="111"/>
-      <c r="S63" s="111"/>
-      <c r="T63" s="113"/>
-      <c r="U63" s="116"/>
-      <c r="V63" s="113"/>
-      <c r="W63" s="116"/>
-      <c r="X63" s="118"/>
-      <c r="Y63" s="111"/>
+      <c r="R63" s="43"/>
+      <c r="S63" s="43"/>
+      <c r="T63" s="49"/>
+      <c r="U63" s="53"/>
+      <c r="V63" s="49"/>
+      <c r="W63" s="53"/>
+      <c r="X63" s="55"/>
+      <c r="Y63" s="43"/>
       <c r="Z63" s="43"/>
       <c r="AA63" s="45"/>
     </row>
     <row r="64" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="42"/>
-      <c r="C64" s="111"/>
-      <c r="D64" s="111"/>
-      <c r="E64" s="111"/>
-      <c r="F64" s="113"/>
-      <c r="G64" s="112"/>
-      <c r="H64" s="113"/>
-      <c r="I64" s="112"/>
-      <c r="J64" s="114"/>
-      <c r="K64" s="111"/>
-      <c r="L64" s="111"/>
-      <c r="M64" s="111"/>
+      <c r="C64" s="43"/>
+      <c r="D64" s="43"/>
+      <c r="E64" s="43"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="48"/>
+      <c r="H64" s="49"/>
+      <c r="I64" s="48"/>
+      <c r="J64" s="51"/>
+      <c r="K64" s="43"/>
+      <c r="L64" s="43"/>
+      <c r="M64" s="43"/>
       <c r="N64" s="43"/>
       <c r="O64" s="43"/>
       <c r="P64" s="43"/>
       <c r="Q64" s="43"/>
-      <c r="R64" s="111"/>
-      <c r="S64" s="111"/>
-      <c r="T64" s="113"/>
-      <c r="U64" s="116"/>
-      <c r="V64" s="113"/>
-      <c r="W64" s="116"/>
-      <c r="X64" s="118"/>
-      <c r="Y64" s="111"/>
+      <c r="R64" s="43"/>
+      <c r="S64" s="43"/>
+      <c r="T64" s="49"/>
+      <c r="U64" s="53"/>
+      <c r="V64" s="49"/>
+      <c r="W64" s="53"/>
+      <c r="X64" s="55"/>
+      <c r="Y64" s="43"/>
       <c r="Z64" s="43"/>
       <c r="AA64" s="45"/>
     </row>
     <row r="65" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="42"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="111"/>
-      <c r="F65" s="113"/>
-      <c r="G65" s="124"/>
-      <c r="H65" s="122"/>
-      <c r="I65" s="124"/>
-      <c r="J65" s="115"/>
-      <c r="K65" s="111"/>
-      <c r="L65" s="111"/>
-      <c r="M65" s="111"/>
+      <c r="C65" s="43"/>
+      <c r="D65" s="43"/>
+      <c r="E65" s="43"/>
+      <c r="F65" s="49"/>
+      <c r="G65" s="57"/>
+      <c r="H65" s="58"/>
+      <c r="I65" s="57"/>
+      <c r="J65" s="52"/>
+      <c r="K65" s="43"/>
+      <c r="L65" s="43"/>
+      <c r="M65" s="43"/>
       <c r="N65" s="43"/>
       <c r="O65" s="43"/>
       <c r="P65" s="43"/>
       <c r="Q65" s="43"/>
-      <c r="R65" s="111"/>
-      <c r="S65" s="111"/>
-      <c r="T65" s="117"/>
-      <c r="U65" s="116"/>
-      <c r="V65" s="113"/>
-      <c r="W65" s="116"/>
-      <c r="X65" s="118"/>
-      <c r="Y65" s="111"/>
+      <c r="R65" s="43"/>
+      <c r="S65" s="43"/>
+      <c r="T65" s="54"/>
+      <c r="U65" s="53"/>
+      <c r="V65" s="49"/>
+      <c r="W65" s="53"/>
+      <c r="X65" s="55"/>
+      <c r="Y65" s="43"/>
       <c r="Z65" s="43"/>
       <c r="AA65" s="45"/>
     </row>
     <row r="66" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="42"/>
-      <c r="C66" s="111"/>
-      <c r="D66" s="111"/>
-      <c r="E66" s="111"/>
-      <c r="F66" s="113"/>
-      <c r="G66" s="124"/>
-      <c r="H66" s="122"/>
-      <c r="I66" s="124"/>
-      <c r="J66" s="115"/>
-      <c r="K66" s="111"/>
-      <c r="L66" s="111"/>
-      <c r="M66" s="111"/>
+      <c r="C66" s="43"/>
+      <c r="D66" s="43"/>
+      <c r="E66" s="43"/>
+      <c r="F66" s="49"/>
+      <c r="G66" s="57"/>
+      <c r="H66" s="58"/>
+      <c r="I66" s="57"/>
+      <c r="J66" s="52"/>
+      <c r="K66" s="43"/>
+      <c r="L66" s="43"/>
+      <c r="M66" s="43"/>
       <c r="N66" s="43"/>
       <c r="O66" s="43"/>
       <c r="P66" s="43"/>
       <c r="Q66" s="43"/>
-      <c r="R66" s="111"/>
-      <c r="S66" s="111"/>
-      <c r="T66" s="117"/>
-      <c r="U66" s="116"/>
-      <c r="V66" s="113"/>
-      <c r="W66" s="116"/>
-      <c r="X66" s="114"/>
-      <c r="Y66" s="111"/>
+      <c r="R66" s="43"/>
+      <c r="S66" s="43"/>
+      <c r="T66" s="54"/>
+      <c r="U66" s="53"/>
+      <c r="V66" s="49"/>
+      <c r="W66" s="53"/>
+      <c r="X66" s="51"/>
+      <c r="Y66" s="43"/>
       <c r="Z66" s="43"/>
       <c r="AA66" s="45"/>
     </row>
     <row r="67" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="42"/>
-      <c r="C67" s="111"/>
-      <c r="D67" s="111"/>
-      <c r="E67" s="111"/>
-      <c r="F67" s="113"/>
-      <c r="G67" s="124"/>
-      <c r="H67" s="122"/>
-      <c r="I67" s="124"/>
-      <c r="J67" s="115"/>
-      <c r="K67" s="111"/>
-      <c r="L67" s="111"/>
-      <c r="M67" s="111"/>
+      <c r="C67" s="43"/>
+      <c r="D67" s="43"/>
+      <c r="E67" s="43"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="58"/>
+      <c r="I67" s="57"/>
+      <c r="J67" s="52"/>
+      <c r="K67" s="43"/>
+      <c r="L67" s="43"/>
+      <c r="M67" s="43"/>
       <c r="N67" s="43"/>
       <c r="O67" s="43"/>
       <c r="P67" s="43"/>
       <c r="Q67" s="43"/>
-      <c r="R67" s="111"/>
-      <c r="S67" s="111"/>
-      <c r="T67" s="117"/>
-      <c r="U67" s="116"/>
-      <c r="V67" s="113"/>
-      <c r="W67" s="116"/>
-      <c r="X67" s="114"/>
-      <c r="Y67" s="111"/>
+      <c r="R67" s="43"/>
+      <c r="S67" s="43"/>
+      <c r="T67" s="54"/>
+      <c r="U67" s="53"/>
+      <c r="V67" s="49"/>
+      <c r="W67" s="53"/>
+      <c r="X67" s="51"/>
+      <c r="Y67" s="43"/>
       <c r="Z67" s="43"/>
       <c r="AA67" s="45"/>
     </row>
     <row r="68" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="42"/>
-      <c r="C68" s="111"/>
-      <c r="D68" s="111"/>
-      <c r="E68" s="111"/>
-      <c r="F68" s="113"/>
-      <c r="G68" s="124"/>
-      <c r="H68" s="122"/>
-      <c r="I68" s="124"/>
-      <c r="J68" s="115"/>
-      <c r="K68" s="111"/>
-      <c r="L68" s="111"/>
-      <c r="M68" s="111"/>
+      <c r="C68" s="43"/>
+      <c r="D68" s="43"/>
+      <c r="E68" s="43"/>
+      <c r="F68" s="49"/>
+      <c r="G68" s="57"/>
+      <c r="H68" s="58"/>
+      <c r="I68" s="57"/>
+      <c r="J68" s="52"/>
+      <c r="K68" s="43"/>
+      <c r="L68" s="43"/>
+      <c r="M68" s="43"/>
       <c r="N68" s="43"/>
       <c r="O68" s="43"/>
       <c r="P68" s="43"/>
       <c r="Q68" s="43"/>
-      <c r="R68" s="111"/>
-      <c r="S68" s="111"/>
-      <c r="T68" s="117"/>
-      <c r="U68" s="118"/>
-      <c r="V68" s="117"/>
-      <c r="W68" s="118"/>
-      <c r="X68" s="114"/>
-      <c r="Y68" s="111"/>
+      <c r="R68" s="43"/>
+      <c r="S68" s="43"/>
+      <c r="T68" s="54"/>
+      <c r="U68" s="55"/>
+      <c r="V68" s="54"/>
+      <c r="W68" s="55"/>
+      <c r="X68" s="51"/>
+      <c r="Y68" s="43"/>
       <c r="Z68" s="43"/>
       <c r="AA68" s="45"/>
     </row>
     <row r="69" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="42"/>
-      <c r="C69" s="111"/>
-      <c r="D69" s="111"/>
-      <c r="E69" s="111"/>
-      <c r="F69" s="113"/>
-      <c r="G69" s="112"/>
-      <c r="H69" s="113"/>
-      <c r="I69" s="112"/>
-      <c r="J69" s="114"/>
-      <c r="K69" s="111"/>
-      <c r="L69" s="111"/>
-      <c r="M69" s="111"/>
+      <c r="C69" s="43"/>
+      <c r="D69" s="43"/>
+      <c r="E69" s="43"/>
+      <c r="F69" s="49"/>
+      <c r="G69" s="48"/>
+      <c r="H69" s="49"/>
+      <c r="I69" s="48"/>
+      <c r="J69" s="51"/>
+      <c r="K69" s="43"/>
+      <c r="L69" s="43"/>
+      <c r="M69" s="43"/>
       <c r="N69" s="43"/>
       <c r="O69" s="43"/>
       <c r="P69" s="43"/>
       <c r="Q69" s="43"/>
-      <c r="R69" s="111"/>
-      <c r="S69" s="111"/>
-      <c r="T69" s="117"/>
-      <c r="U69" s="118"/>
-      <c r="V69" s="117"/>
-      <c r="W69" s="118"/>
-      <c r="X69" s="114"/>
-      <c r="Y69" s="111"/>
+      <c r="R69" s="43"/>
+      <c r="S69" s="43"/>
+      <c r="T69" s="54"/>
+      <c r="U69" s="55"/>
+      <c r="V69" s="54"/>
+      <c r="W69" s="55"/>
+      <c r="X69" s="51"/>
+      <c r="Y69" s="43"/>
       <c r="Z69" s="43"/>
       <c r="AA69" s="45"/>
     </row>
     <row r="70" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="42"/>
-      <c r="C70" s="111"/>
-      <c r="D70" s="111"/>
-      <c r="E70" s="111"/>
-      <c r="F70" s="113"/>
-      <c r="G70" s="112"/>
-      <c r="H70" s="113"/>
-      <c r="I70" s="112"/>
-      <c r="J70" s="114"/>
-      <c r="K70" s="111"/>
-      <c r="L70" s="111"/>
-      <c r="M70" s="111"/>
+      <c r="C70" s="43"/>
+      <c r="D70" s="43"/>
+      <c r="E70" s="43"/>
+      <c r="F70" s="49"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="49"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="51"/>
+      <c r="K70" s="43"/>
+      <c r="L70" s="43"/>
+      <c r="M70" s="43"/>
       <c r="N70" s="43"/>
       <c r="O70" s="43"/>
       <c r="P70" s="43"/>
       <c r="Q70" s="43"/>
-      <c r="R70" s="111"/>
-      <c r="S70" s="111"/>
-      <c r="T70" s="117"/>
-      <c r="U70" s="118"/>
-      <c r="V70" s="117"/>
-      <c r="W70" s="118"/>
-      <c r="X70" s="114"/>
-      <c r="Y70" s="111"/>
+      <c r="R70" s="43"/>
+      <c r="S70" s="43"/>
+      <c r="T70" s="54"/>
+      <c r="U70" s="55"/>
+      <c r="V70" s="54"/>
+      <c r="W70" s="55"/>
+      <c r="X70" s="51"/>
+      <c r="Y70" s="43"/>
       <c r="Z70" s="43"/>
       <c r="AA70" s="45"/>
     </row>
     <row r="71" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="42"/>
-      <c r="C71" s="111"/>
-      <c r="D71" s="111"/>
-      <c r="E71" s="111"/>
-      <c r="F71" s="111"/>
-      <c r="G71" s="111"/>
-      <c r="H71" s="111"/>
-      <c r="I71" s="111"/>
-      <c r="J71" s="111"/>
-      <c r="K71" s="111"/>
-      <c r="L71" s="111"/>
-      <c r="M71" s="111"/>
+      <c r="C71" s="43"/>
+      <c r="D71" s="43"/>
+      <c r="E71" s="43"/>
+      <c r="F71" s="43"/>
+      <c r="G71" s="43"/>
+      <c r="H71" s="43"/>
+      <c r="I71" s="43"/>
+      <c r="J71" s="43"/>
+      <c r="K71" s="43"/>
+      <c r="L71" s="43"/>
+      <c r="M71" s="43"/>
       <c r="N71" s="43"/>
       <c r="O71" s="43"/>
       <c r="P71" s="43"/>
       <c r="Q71" s="43"/>
-      <c r="R71" s="111"/>
-      <c r="S71" s="111"/>
-      <c r="T71" s="117"/>
-      <c r="U71" s="118"/>
-      <c r="V71" s="117"/>
-      <c r="W71" s="118"/>
-      <c r="X71" s="126"/>
-      <c r="Y71" s="111"/>
+      <c r="R71" s="43"/>
+      <c r="S71" s="43"/>
+      <c r="T71" s="54"/>
+      <c r="U71" s="55"/>
+      <c r="V71" s="54"/>
+      <c r="W71" s="55"/>
+      <c r="X71" s="59"/>
+      <c r="Y71" s="43"/>
       <c r="Z71" s="43"/>
       <c r="AA71" s="45"/>
     </row>
     <row r="72" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="42"/>
-      <c r="C72" s="111"/>
-      <c r="D72" s="111"/>
-      <c r="E72" s="111"/>
-      <c r="F72" s="111"/>
-      <c r="G72" s="111"/>
-      <c r="H72" s="111"/>
-      <c r="I72" s="111"/>
-      <c r="J72" s="111"/>
-      <c r="K72" s="111"/>
-      <c r="L72" s="111"/>
-      <c r="M72" s="111"/>
+      <c r="C72" s="43"/>
+      <c r="D72" s="43"/>
+      <c r="E72" s="43"/>
+      <c r="F72" s="43"/>
+      <c r="G72" s="43"/>
+      <c r="H72" s="43"/>
+      <c r="I72" s="43"/>
+      <c r="J72" s="43"/>
+      <c r="K72" s="43"/>
+      <c r="L72" s="43"/>
+      <c r="M72" s="43"/>
       <c r="N72" s="43"/>
       <c r="O72" s="43"/>
       <c r="P72" s="43"/>
       <c r="Q72" s="43"/>
-      <c r="R72" s="111"/>
-      <c r="S72" s="111"/>
-      <c r="T72" s="111"/>
-      <c r="U72" s="111"/>
-      <c r="V72" s="111"/>
-      <c r="W72" s="111"/>
-      <c r="X72" s="111"/>
-      <c r="Y72" s="111"/>
+      <c r="R72" s="43"/>
+      <c r="S72" s="43"/>
+      <c r="T72" s="43"/>
+      <c r="U72" s="43"/>
+      <c r="V72" s="43"/>
+      <c r="W72" s="43"/>
+      <c r="X72" s="43"/>
+      <c r="Y72" s="43"/>
       <c r="Z72" s="43"/>
       <c r="AA72" s="45"/>
     </row>
@@ -5567,683 +5059,673 @@
       <c r="P81" s="43"/>
       <c r="Q81" s="43"/>
       <c r="R81" s="45"/>
-      <c r="S81" s="54"/>
-      <c r="T81" s="55"/>
-      <c r="U81" s="55"/>
-      <c r="V81" s="55"/>
-      <c r="W81" s="55"/>
-      <c r="X81" s="55"/>
-      <c r="Y81" s="55"/>
-      <c r="Z81" s="55"/>
-      <c r="AA81" s="56"/>
+      <c r="S81" s="60"/>
+      <c r="T81" s="61"/>
+      <c r="U81" s="61"/>
+      <c r="V81" s="61"/>
+      <c r="W81" s="61"/>
+      <c r="X81" s="61"/>
+      <c r="Y81" s="61"/>
+      <c r="Z81" s="61"/>
+      <c r="AA81" s="62"/>
     </row>
     <row r="82" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="95" t="s">
-        <v>175</v>
-      </c>
-      <c r="C82" s="96"/>
-      <c r="D82" s="96"/>
-      <c r="E82" s="96"/>
-      <c r="F82" s="96"/>
-      <c r="G82" s="96"/>
-      <c r="H82" s="96"/>
-      <c r="I82" s="96"/>
-      <c r="J82" s="96"/>
-      <c r="K82" s="96"/>
-      <c r="L82" s="96"/>
-      <c r="M82" s="96"/>
-      <c r="N82" s="96"/>
-      <c r="O82" s="96"/>
-      <c r="P82" s="96"/>
-      <c r="Q82" s="96"/>
-      <c r="R82" s="97"/>
-      <c r="S82" s="88"/>
-      <c r="T82" s="89"/>
-      <c r="U82" s="89"/>
-      <c r="V82" s="89"/>
-      <c r="W82" s="89"/>
-      <c r="X82" s="89"/>
-      <c r="Y82" s="89"/>
-      <c r="Z82" s="89"/>
-      <c r="AA82" s="89"/>
+      <c r="B82" s="100" t="s">
+        <v>164</v>
+      </c>
+      <c r="C82" s="101"/>
+      <c r="D82" s="101"/>
+      <c r="E82" s="101"/>
+      <c r="F82" s="101"/>
+      <c r="G82" s="101"/>
+      <c r="H82" s="101"/>
+      <c r="I82" s="101"/>
+      <c r="J82" s="101"/>
+      <c r="K82" s="101"/>
+      <c r="L82" s="101"/>
+      <c r="M82" s="101"/>
+      <c r="N82" s="101"/>
+      <c r="O82" s="101"/>
+      <c r="P82" s="101"/>
+      <c r="Q82" s="101"/>
+      <c r="R82" s="102"/>
+      <c r="S82" s="94"/>
+      <c r="T82" s="95"/>
+      <c r="U82" s="95"/>
+      <c r="V82" s="95"/>
+      <c r="W82" s="95"/>
+      <c r="X82" s="95"/>
+      <c r="Y82" s="95"/>
+      <c r="Z82" s="95"/>
+      <c r="AA82" s="95"/>
     </row>
     <row r="83" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="98"/>
-      <c r="C83" s="99"/>
-      <c r="D83" s="99"/>
-      <c r="E83" s="99"/>
-      <c r="F83" s="99"/>
-      <c r="G83" s="99"/>
-      <c r="H83" s="99"/>
-      <c r="I83" s="99"/>
-      <c r="J83" s="99"/>
-      <c r="K83" s="99"/>
-      <c r="L83" s="57"/>
-      <c r="M83" s="57"/>
-      <c r="N83" s="57"/>
-      <c r="O83" s="57"/>
-      <c r="P83" s="57"/>
+      <c r="B83" s="103"/>
+      <c r="C83" s="104"/>
+      <c r="D83" s="104"/>
+      <c r="E83" s="104"/>
+      <c r="F83" s="104"/>
+      <c r="G83" s="104"/>
+      <c r="H83" s="104"/>
+      <c r="I83" s="104"/>
+      <c r="J83" s="104"/>
+      <c r="K83" s="104"/>
+      <c r="L83" s="63"/>
+      <c r="M83" s="63"/>
+      <c r="N83" s="63"/>
+      <c r="O83" s="63"/>
+      <c r="P83" s="63"/>
       <c r="Q83" s="21"/>
       <c r="R83" s="22"/>
-      <c r="T83" s="58"/>
-      <c r="U83" s="59" t="s">
-        <v>176</v>
-      </c>
-      <c r="V83" s="60">
-        <v>211</v>
-      </c>
-      <c r="W83" s="61"/>
+      <c r="T83" s="64"/>
+      <c r="U83" s="65" t="s">
+        <v>165</v>
+      </c>
+      <c r="V83" s="66"/>
+      <c r="W83" s="67"/>
     </row>
     <row r="84" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="98"/>
-      <c r="C84" s="99"/>
-      <c r="D84" s="99"/>
-      <c r="E84" s="99"/>
-      <c r="F84" s="99"/>
-      <c r="G84" s="99"/>
-      <c r="H84" s="99"/>
-      <c r="I84" s="99"/>
-      <c r="J84" s="99"/>
-      <c r="K84" s="99"/>
-      <c r="L84" s="57"/>
-      <c r="M84" s="57"/>
-      <c r="N84" s="57"/>
-      <c r="O84" s="57"/>
-      <c r="P84" s="57"/>
+      <c r="B84" s="103"/>
+      <c r="C84" s="104"/>
+      <c r="D84" s="104"/>
+      <c r="E84" s="104"/>
+      <c r="F84" s="104"/>
+      <c r="G84" s="104"/>
+      <c r="H84" s="104"/>
+      <c r="I84" s="104"/>
+      <c r="J84" s="104"/>
+      <c r="K84" s="104"/>
+      <c r="L84" s="63"/>
+      <c r="M84" s="63"/>
+      <c r="N84" s="63"/>
+      <c r="O84" s="63"/>
+      <c r="P84" s="63"/>
       <c r="Q84" s="21"/>
       <c r="R84" s="22"/>
-      <c r="T84" s="62"/>
-      <c r="U84" s="63"/>
-      <c r="V84" s="63"/>
-      <c r="W84" s="64"/>
+      <c r="T84" s="68"/>
+      <c r="U84" s="69"/>
+      <c r="V84" s="69"/>
+      <c r="W84" s="70"/>
     </row>
     <row r="85" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="98"/>
-      <c r="C85" s="99"/>
-      <c r="D85" s="99"/>
-      <c r="E85" s="99"/>
-      <c r="F85" s="99"/>
-      <c r="G85" s="99"/>
-      <c r="H85" s="99"/>
-      <c r="I85" s="99"/>
-      <c r="J85" s="99"/>
-      <c r="K85" s="99"/>
-      <c r="L85" s="57"/>
-      <c r="M85" s="57"/>
-      <c r="N85" s="57"/>
-      <c r="O85" s="57"/>
-      <c r="P85" s="57"/>
+      <c r="B85" s="103"/>
+      <c r="C85" s="104"/>
+      <c r="D85" s="104"/>
+      <c r="E85" s="104"/>
+      <c r="F85" s="104"/>
+      <c r="G85" s="104"/>
+      <c r="H85" s="104"/>
+      <c r="I85" s="104"/>
+      <c r="J85" s="104"/>
+      <c r="K85" s="104"/>
+      <c r="L85" s="63"/>
+      <c r="M85" s="63"/>
+      <c r="N85" s="63"/>
+      <c r="O85" s="63"/>
+      <c r="P85" s="63"/>
       <c r="Q85" s="21"/>
       <c r="R85" s="22"/>
-      <c r="T85" s="62"/>
-      <c r="U85" s="65" t="s">
-        <v>177</v>
-      </c>
-      <c r="V85" s="66" t="s">
-        <v>111</v>
-      </c>
-      <c r="W85" s="64"/>
+      <c r="T85" s="68"/>
+      <c r="U85" s="71" t="s">
+        <v>166</v>
+      </c>
+      <c r="V85" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="W85" s="70"/>
     </row>
     <row r="86" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="98"/>
-      <c r="C86" s="99"/>
-      <c r="D86" s="99"/>
-      <c r="E86" s="99"/>
-      <c r="F86" s="99"/>
-      <c r="G86" s="99"/>
-      <c r="H86" s="99"/>
-      <c r="I86" s="99"/>
-      <c r="J86" s="99"/>
-      <c r="K86" s="99"/>
-      <c r="L86" s="57"/>
-      <c r="M86" s="57"/>
-      <c r="N86" s="57"/>
-      <c r="O86" s="57"/>
-      <c r="P86" s="57"/>
+      <c r="B86" s="103"/>
+      <c r="C86" s="104"/>
+      <c r="D86" s="104"/>
+      <c r="E86" s="104"/>
+      <c r="F86" s="104"/>
+      <c r="G86" s="104"/>
+      <c r="H86" s="104"/>
+      <c r="I86" s="104"/>
+      <c r="J86" s="104"/>
+      <c r="K86" s="104"/>
+      <c r="L86" s="63"/>
+      <c r="M86" s="63"/>
+      <c r="N86" s="63"/>
+      <c r="O86" s="63"/>
+      <c r="P86" s="63"/>
       <c r="Q86" s="21"/>
       <c r="R86" s="22"/>
-      <c r="T86" s="62"/>
-      <c r="U86" s="67" t="s">
-        <v>178</v>
+      <c r="T86" s="68"/>
+      <c r="U86" s="73" t="s">
+        <v>167</v>
       </c>
       <c r="V86" s="11"/>
-      <c r="W86" s="64"/>
+      <c r="W86" s="70"/>
     </row>
     <row r="87" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="98"/>
-      <c r="C87" s="99"/>
-      <c r="D87" s="99"/>
-      <c r="E87" s="99"/>
-      <c r="F87" s="99"/>
-      <c r="G87" s="99"/>
-      <c r="H87" s="99"/>
-      <c r="I87" s="99"/>
-      <c r="J87" s="99"/>
-      <c r="K87" s="99"/>
-      <c r="L87" s="57"/>
-      <c r="M87" s="57"/>
-      <c r="N87" s="57"/>
-      <c r="O87" s="57"/>
-      <c r="P87" s="57"/>
+      <c r="B87" s="103"/>
+      <c r="C87" s="104"/>
+      <c r="D87" s="104"/>
+      <c r="E87" s="104"/>
+      <c r="F87" s="104"/>
+      <c r="G87" s="104"/>
+      <c r="H87" s="104"/>
+      <c r="I87" s="104"/>
+      <c r="J87" s="104"/>
+      <c r="K87" s="104"/>
+      <c r="L87" s="63"/>
+      <c r="M87" s="63"/>
+      <c r="N87" s="63"/>
+      <c r="O87" s="63"/>
+      <c r="P87" s="63"/>
       <c r="Q87" s="21"/>
       <c r="R87" s="22"/>
-      <c r="T87" s="62"/>
-      <c r="U87" s="68" t="s">
-        <v>179</v>
-      </c>
-      <c r="V87" s="69"/>
-      <c r="W87" s="64"/>
+      <c r="T87" s="68"/>
+      <c r="U87" s="74" t="s">
+        <v>168</v>
+      </c>
+      <c r="V87" s="75"/>
+      <c r="W87" s="70"/>
     </row>
     <row r="88" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="98"/>
-      <c r="C88" s="99"/>
-      <c r="D88" s="99"/>
-      <c r="E88" s="99"/>
-      <c r="F88" s="99"/>
-      <c r="G88" s="99"/>
-      <c r="H88" s="99"/>
-      <c r="I88" s="99"/>
-      <c r="J88" s="99"/>
-      <c r="K88" s="99"/>
-      <c r="L88" s="57"/>
-      <c r="M88" s="57"/>
-      <c r="N88" s="57"/>
-      <c r="O88" s="57"/>
-      <c r="P88" s="57"/>
+      <c r="B88" s="103"/>
+      <c r="C88" s="104"/>
+      <c r="D88" s="104"/>
+      <c r="E88" s="104"/>
+      <c r="F88" s="104"/>
+      <c r="G88" s="104"/>
+      <c r="H88" s="104"/>
+      <c r="I88" s="104"/>
+      <c r="J88" s="104"/>
+      <c r="K88" s="104"/>
+      <c r="L88" s="63"/>
+      <c r="M88" s="63"/>
+      <c r="N88" s="63"/>
+      <c r="O88" s="63"/>
+      <c r="P88" s="63"/>
       <c r="Q88" s="21"/>
       <c r="R88" s="22"/>
-      <c r="T88" s="62"/>
-      <c r="U88" s="63"/>
-      <c r="V88" s="63"/>
-      <c r="W88" s="64"/>
+      <c r="T88" s="68"/>
+      <c r="U88" s="69"/>
+      <c r="V88" s="69"/>
+      <c r="W88" s="70"/>
     </row>
     <row r="89" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="98"/>
-      <c r="C89" s="99"/>
-      <c r="D89" s="99"/>
-      <c r="E89" s="99"/>
-      <c r="F89" s="99"/>
-      <c r="G89" s="99"/>
-      <c r="H89" s="99"/>
-      <c r="I89" s="99"/>
-      <c r="J89" s="99"/>
-      <c r="K89" s="99"/>
-      <c r="L89" s="57"/>
-      <c r="M89" s="57"/>
-      <c r="N89" s="57"/>
-      <c r="O89" s="57"/>
-      <c r="P89" s="57"/>
+      <c r="B89" s="103"/>
+      <c r="C89" s="104"/>
+      <c r="D89" s="104"/>
+      <c r="E89" s="104"/>
+      <c r="F89" s="104"/>
+      <c r="G89" s="104"/>
+      <c r="H89" s="104"/>
+      <c r="I89" s="104"/>
+      <c r="J89" s="104"/>
+      <c r="K89" s="104"/>
+      <c r="L89" s="63"/>
+      <c r="M89" s="63"/>
+      <c r="N89" s="63"/>
+      <c r="O89" s="63"/>
+      <c r="P89" s="63"/>
       <c r="Q89" s="21"/>
       <c r="R89" s="22"/>
-      <c r="T89" s="62"/>
-      <c r="U89" s="65" t="s">
-        <v>177</v>
-      </c>
-      <c r="V89" s="66" t="s">
+      <c r="T89" s="68"/>
+      <c r="U89" s="71" t="s">
+        <v>166</v>
+      </c>
+      <c r="V89" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="W89" s="64"/>
+      <c r="W89" s="70"/>
     </row>
     <row r="90" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="98"/>
-      <c r="C90" s="99"/>
-      <c r="D90" s="99"/>
-      <c r="E90" s="99"/>
-      <c r="F90" s="99"/>
-      <c r="G90" s="99"/>
-      <c r="H90" s="99"/>
-      <c r="I90" s="99"/>
-      <c r="J90" s="99"/>
-      <c r="K90" s="99"/>
-      <c r="L90" s="57"/>
-      <c r="M90" s="57"/>
-      <c r="N90" s="57"/>
-      <c r="O90" s="57"/>
-      <c r="P90" s="57"/>
+      <c r="B90" s="103"/>
+      <c r="C90" s="104"/>
+      <c r="D90" s="104"/>
+      <c r="E90" s="104"/>
+      <c r="F90" s="104"/>
+      <c r="G90" s="104"/>
+      <c r="H90" s="104"/>
+      <c r="I90" s="104"/>
+      <c r="J90" s="104"/>
+      <c r="K90" s="104"/>
+      <c r="L90" s="63"/>
+      <c r="M90" s="63"/>
+      <c r="N90" s="63"/>
+      <c r="O90" s="63"/>
+      <c r="P90" s="63"/>
       <c r="Q90" s="21"/>
       <c r="R90" s="22"/>
-      <c r="T90" s="62"/>
-      <c r="U90" s="70" t="s">
-        <v>179</v>
-      </c>
-      <c r="V90" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="W90" s="64"/>
+      <c r="T90" s="68"/>
+      <c r="U90" s="76" t="s">
+        <v>168</v>
+      </c>
+      <c r="V90" s="11"/>
+      <c r="W90" s="70"/>
     </row>
     <row r="91" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="98"/>
-      <c r="C91" s="99"/>
-      <c r="D91" s="99"/>
-      <c r="E91" s="99"/>
-      <c r="F91" s="99"/>
-      <c r="G91" s="99"/>
-      <c r="H91" s="99"/>
-      <c r="I91" s="99"/>
-      <c r="J91" s="99"/>
-      <c r="K91" s="99"/>
-      <c r="L91" s="57"/>
-      <c r="M91" s="57"/>
-      <c r="N91" s="57"/>
-      <c r="O91" s="57"/>
-      <c r="P91" s="57"/>
+      <c r="B91" s="103"/>
+      <c r="C91" s="104"/>
+      <c r="D91" s="104"/>
+      <c r="E91" s="104"/>
+      <c r="F91" s="104"/>
+      <c r="G91" s="104"/>
+      <c r="H91" s="104"/>
+      <c r="I91" s="104"/>
+      <c r="J91" s="104"/>
+      <c r="K91" s="104"/>
+      <c r="L91" s="63"/>
+      <c r="M91" s="63"/>
+      <c r="N91" s="63"/>
+      <c r="O91" s="63"/>
+      <c r="P91" s="63"/>
       <c r="Q91" s="21"/>
       <c r="R91" s="22"/>
-      <c r="T91" s="62"/>
-      <c r="U91" s="70" t="s">
-        <v>181</v>
-      </c>
-      <c r="V91" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="W91" s="64"/>
+      <c r="T91" s="68"/>
+      <c r="U91" s="76" t="s">
+        <v>169</v>
+      </c>
+      <c r="V91" s="11"/>
+      <c r="W91" s="70"/>
     </row>
     <row r="92" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="98"/>
-      <c r="C92" s="99"/>
-      <c r="D92" s="99"/>
-      <c r="E92" s="99"/>
-      <c r="F92" s="99"/>
-      <c r="G92" s="99"/>
-      <c r="H92" s="99"/>
-      <c r="I92" s="99"/>
-      <c r="J92" s="99"/>
-      <c r="K92" s="99"/>
-      <c r="L92" s="57"/>
-      <c r="M92" s="57"/>
-      <c r="N92" s="57"/>
-      <c r="O92" s="57"/>
-      <c r="P92" s="57"/>
+      <c r="B92" s="103"/>
+      <c r="C92" s="104"/>
+      <c r="D92" s="104"/>
+      <c r="E92" s="104"/>
+      <c r="F92" s="104"/>
+      <c r="G92" s="104"/>
+      <c r="H92" s="104"/>
+      <c r="I92" s="104"/>
+      <c r="J92" s="104"/>
+      <c r="K92" s="104"/>
+      <c r="L92" s="63"/>
+      <c r="M92" s="63"/>
+      <c r="N92" s="63"/>
+      <c r="O92" s="63"/>
+      <c r="P92" s="63"/>
       <c r="Q92" s="21"/>
       <c r="R92" s="22"/>
-      <c r="T92" s="62"/>
-      <c r="U92" s="71" t="s">
-        <v>182</v>
-      </c>
-      <c r="V92" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="W92" s="64"/>
+      <c r="T92" s="68"/>
+      <c r="U92" s="77" t="s">
+        <v>170</v>
+      </c>
+      <c r="V92" s="11"/>
+      <c r="W92" s="70"/>
     </row>
     <row r="93" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="98"/>
-      <c r="C93" s="99"/>
-      <c r="D93" s="99"/>
-      <c r="E93" s="99"/>
-      <c r="F93" s="99"/>
-      <c r="G93" s="99"/>
-      <c r="H93" s="99"/>
-      <c r="I93" s="99"/>
-      <c r="J93" s="99"/>
-      <c r="K93" s="99"/>
-      <c r="L93" s="57"/>
-      <c r="M93" s="57"/>
-      <c r="N93" s="57"/>
-      <c r="O93" s="57"/>
-      <c r="P93" s="57"/>
+      <c r="B93" s="103"/>
+      <c r="C93" s="104"/>
+      <c r="D93" s="104"/>
+      <c r="E93" s="104"/>
+      <c r="F93" s="104"/>
+      <c r="G93" s="104"/>
+      <c r="H93" s="104"/>
+      <c r="I93" s="104"/>
+      <c r="J93" s="104"/>
+      <c r="K93" s="104"/>
+      <c r="L93" s="63"/>
+      <c r="M93" s="63"/>
+      <c r="N93" s="63"/>
+      <c r="O93" s="63"/>
+      <c r="P93" s="63"/>
       <c r="Q93" s="21"/>
       <c r="R93" s="22"/>
-      <c r="T93" s="62"/>
-      <c r="U93" s="68" t="s">
-        <v>183</v>
-      </c>
-      <c r="V93" s="69" t="s">
-        <v>184</v>
-      </c>
-      <c r="W93" s="64"/>
+      <c r="T93" s="68"/>
+      <c r="U93" s="74" t="s">
+        <v>171</v>
+      </c>
+      <c r="V93" s="75"/>
+      <c r="W93" s="70"/>
     </row>
     <row r="94" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="98"/>
-      <c r="C94" s="99"/>
-      <c r="D94" s="99"/>
-      <c r="E94" s="99"/>
-      <c r="F94" s="99"/>
-      <c r="G94" s="99"/>
-      <c r="H94" s="99"/>
-      <c r="I94" s="99"/>
-      <c r="J94" s="99"/>
-      <c r="K94" s="99"/>
-      <c r="L94" s="57"/>
-      <c r="M94" s="57"/>
-      <c r="N94" s="57"/>
-      <c r="O94" s="57"/>
-      <c r="P94" s="57"/>
+      <c r="B94" s="103"/>
+      <c r="C94" s="104"/>
+      <c r="D94" s="104"/>
+      <c r="E94" s="104"/>
+      <c r="F94" s="104"/>
+      <c r="G94" s="104"/>
+      <c r="H94" s="104"/>
+      <c r="I94" s="104"/>
+      <c r="J94" s="104"/>
+      <c r="K94" s="104"/>
+      <c r="L94" s="63"/>
+      <c r="M94" s="63"/>
+      <c r="N94" s="63"/>
+      <c r="O94" s="63"/>
+      <c r="P94" s="63"/>
       <c r="Q94" s="21"/>
       <c r="R94" s="22"/>
-      <c r="T94" s="62"/>
-      <c r="U94" s="63"/>
-      <c r="V94" s="63"/>
-      <c r="W94" s="64"/>
+      <c r="T94" s="68"/>
+      <c r="U94" s="69"/>
+      <c r="V94" s="69"/>
+      <c r="W94" s="70"/>
     </row>
     <row r="95" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="98"/>
-      <c r="C95" s="99"/>
-      <c r="D95" s="99"/>
-      <c r="E95" s="99"/>
-      <c r="F95" s="99"/>
-      <c r="G95" s="99"/>
-      <c r="H95" s="99"/>
-      <c r="I95" s="99"/>
-      <c r="J95" s="99"/>
-      <c r="K95" s="99"/>
-      <c r="L95" s="57"/>
-      <c r="M95" s="57"/>
-      <c r="N95" s="57"/>
-      <c r="O95" s="57"/>
-      <c r="P95" s="57"/>
+      <c r="B95" s="103"/>
+      <c r="C95" s="104"/>
+      <c r="D95" s="104"/>
+      <c r="E95" s="104"/>
+      <c r="F95" s="104"/>
+      <c r="G95" s="104"/>
+      <c r="H95" s="104"/>
+      <c r="I95" s="104"/>
+      <c r="J95" s="104"/>
+      <c r="K95" s="104"/>
+      <c r="L95" s="63"/>
+      <c r="M95" s="63"/>
+      <c r="N95" s="63"/>
+      <c r="O95" s="63"/>
+      <c r="P95" s="63"/>
       <c r="Q95" s="21"/>
       <c r="R95" s="22"/>
-      <c r="T95" s="62"/>
-      <c r="U95" s="65" t="s">
-        <v>177</v>
-      </c>
-      <c r="V95" s="66" t="s">
-        <v>185</v>
-      </c>
-      <c r="W95" s="64"/>
+      <c r="T95" s="68"/>
+      <c r="U95" s="71" t="s">
+        <v>166</v>
+      </c>
+      <c r="V95" s="72" t="s">
+        <v>172</v>
+      </c>
+      <c r="W95" s="70"/>
     </row>
     <row r="96" spans="2:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="98"/>
-      <c r="C96" s="99"/>
-      <c r="D96" s="99"/>
-      <c r="E96" s="99"/>
-      <c r="F96" s="99"/>
-      <c r="G96" s="99"/>
-      <c r="H96" s="99"/>
-      <c r="I96" s="99"/>
-      <c r="J96" s="99"/>
-      <c r="K96" s="99"/>
-      <c r="L96" s="57"/>
-      <c r="M96" s="57"/>
-      <c r="N96" s="57"/>
-      <c r="O96" s="57"/>
-      <c r="P96" s="57"/>
+      <c r="B96" s="103"/>
+      <c r="C96" s="104"/>
+      <c r="D96" s="104"/>
+      <c r="E96" s="104"/>
+      <c r="F96" s="104"/>
+      <c r="G96" s="104"/>
+      <c r="H96" s="104"/>
+      <c r="I96" s="104"/>
+      <c r="J96" s="104"/>
+      <c r="K96" s="104"/>
+      <c r="L96" s="63"/>
+      <c r="M96" s="63"/>
+      <c r="N96" s="63"/>
+      <c r="O96" s="63"/>
+      <c r="P96" s="63"/>
       <c r="Q96" s="21"/>
       <c r="R96" s="22"/>
-      <c r="T96" s="62"/>
-      <c r="U96" s="72" t="s">
-        <v>183</v>
-      </c>
-      <c r="V96" s="69"/>
-      <c r="W96" s="64"/>
+      <c r="T96" s="68"/>
+      <c r="U96" s="78" t="s">
+        <v>171</v>
+      </c>
+      <c r="V96" s="75"/>
+      <c r="W96" s="70"/>
     </row>
     <row r="97" spans="2:23" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="98"/>
-      <c r="C97" s="99"/>
-      <c r="D97" s="99"/>
-      <c r="E97" s="99"/>
-      <c r="F97" s="99"/>
-      <c r="G97" s="99"/>
-      <c r="H97" s="99"/>
-      <c r="I97" s="99"/>
-      <c r="J97" s="99"/>
-      <c r="K97" s="99"/>
-      <c r="L97" s="57"/>
-      <c r="M97" s="57"/>
-      <c r="N97" s="57"/>
-      <c r="O97" s="57"/>
-      <c r="P97" s="57"/>
+      <c r="B97" s="103"/>
+      <c r="C97" s="104"/>
+      <c r="D97" s="104"/>
+      <c r="E97" s="104"/>
+      <c r="F97" s="104"/>
+      <c r="G97" s="104"/>
+      <c r="H97" s="104"/>
+      <c r="I97" s="104"/>
+      <c r="J97" s="104"/>
+      <c r="K97" s="104"/>
+      <c r="L97" s="63"/>
+      <c r="M97" s="63"/>
+      <c r="N97" s="63"/>
+      <c r="O97" s="63"/>
+      <c r="P97" s="63"/>
       <c r="Q97" s="21"/>
       <c r="R97" s="22"/>
-      <c r="T97" s="62"/>
-      <c r="U97" s="63"/>
-      <c r="V97" s="63"/>
-      <c r="W97" s="64"/>
+      <c r="T97" s="68"/>
+      <c r="U97" s="69"/>
+      <c r="V97" s="69"/>
+      <c r="W97" s="70"/>
     </row>
     <row r="98" spans="2:23" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="98"/>
-      <c r="C98" s="99"/>
-      <c r="D98" s="99"/>
-      <c r="E98" s="99"/>
-      <c r="F98" s="99"/>
-      <c r="G98" s="99"/>
-      <c r="H98" s="99"/>
-      <c r="I98" s="99"/>
-      <c r="J98" s="99"/>
-      <c r="K98" s="99"/>
-      <c r="L98" s="57"/>
-      <c r="M98" s="57"/>
-      <c r="N98" s="57"/>
-      <c r="O98" s="57"/>
-      <c r="P98" s="57"/>
+      <c r="B98" s="103"/>
+      <c r="C98" s="104"/>
+      <c r="D98" s="104"/>
+      <c r="E98" s="104"/>
+      <c r="F98" s="104"/>
+      <c r="G98" s="104"/>
+      <c r="H98" s="104"/>
+      <c r="I98" s="104"/>
+      <c r="J98" s="104"/>
+      <c r="K98" s="104"/>
+      <c r="L98" s="63"/>
+      <c r="M98" s="63"/>
+      <c r="N98" s="63"/>
+      <c r="O98" s="63"/>
+      <c r="P98" s="63"/>
       <c r="Q98" s="21"/>
       <c r="R98" s="22"/>
-      <c r="T98" s="62"/>
-      <c r="U98" s="65" t="s">
-        <v>177</v>
-      </c>
-      <c r="V98" s="66" t="s">
+      <c r="T98" s="68"/>
+      <c r="U98" s="71" t="s">
+        <v>166</v>
+      </c>
+      <c r="V98" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="W98" s="64"/>
+      <c r="W98" s="70"/>
     </row>
     <row r="99" spans="2:23" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="98"/>
-      <c r="C99" s="99"/>
-      <c r="D99" s="99"/>
-      <c r="E99" s="99"/>
-      <c r="F99" s="99"/>
-      <c r="G99" s="99"/>
-      <c r="H99" s="99"/>
-      <c r="I99" s="99"/>
-      <c r="J99" s="99"/>
-      <c r="K99" s="99"/>
-      <c r="L99" s="57"/>
-      <c r="M99" s="57"/>
-      <c r="N99" s="57"/>
-      <c r="O99" s="57"/>
-      <c r="P99" s="57"/>
+      <c r="B99" s="103"/>
+      <c r="C99" s="104"/>
+      <c r="D99" s="104"/>
+      <c r="E99" s="104"/>
+      <c r="F99" s="104"/>
+      <c r="G99" s="104"/>
+      <c r="H99" s="104"/>
+      <c r="I99" s="104"/>
+      <c r="J99" s="104"/>
+      <c r="K99" s="104"/>
+      <c r="L99" s="63"/>
+      <c r="M99" s="63"/>
+      <c r="N99" s="63"/>
+      <c r="O99" s="63"/>
+      <c r="P99" s="63"/>
       <c r="Q99" s="21"/>
       <c r="R99" s="22"/>
-      <c r="T99" s="62"/>
-      <c r="U99" s="70" t="s">
-        <v>186</v>
+      <c r="T99" s="68"/>
+      <c r="U99" s="76" t="s">
+        <v>173</v>
       </c>
       <c r="V99" s="11"/>
-      <c r="W99" s="64"/>
+      <c r="W99" s="70"/>
     </row>
     <row r="100" spans="2:23" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="98"/>
-      <c r="C100" s="99"/>
-      <c r="D100" s="99"/>
-      <c r="E100" s="99"/>
-      <c r="F100" s="99"/>
-      <c r="G100" s="99"/>
-      <c r="H100" s="99"/>
-      <c r="I100" s="99"/>
-      <c r="J100" s="99"/>
-      <c r="K100" s="99"/>
-      <c r="L100" s="57"/>
-      <c r="M100" s="57"/>
-      <c r="N100" s="57"/>
-      <c r="O100" s="57"/>
-      <c r="P100" s="57"/>
+      <c r="B100" s="103"/>
+      <c r="C100" s="104"/>
+      <c r="D100" s="104"/>
+      <c r="E100" s="104"/>
+      <c r="F100" s="104"/>
+      <c r="G100" s="104"/>
+      <c r="H100" s="104"/>
+      <c r="I100" s="104"/>
+      <c r="J100" s="104"/>
+      <c r="K100" s="104"/>
+      <c r="L100" s="63"/>
+      <c r="M100" s="63"/>
+      <c r="N100" s="63"/>
+      <c r="O100" s="63"/>
+      <c r="P100" s="63"/>
       <c r="Q100" s="21"/>
       <c r="R100" s="22"/>
-      <c r="T100" s="62"/>
-      <c r="U100" s="67" t="s">
-        <v>187</v>
+      <c r="T100" s="68"/>
+      <c r="U100" s="73" t="s">
+        <v>174</v>
       </c>
       <c r="V100" s="11"/>
-      <c r="W100" s="64"/>
+      <c r="W100" s="70"/>
     </row>
     <row r="101" spans="2:23" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="100"/>
-      <c r="C101" s="101"/>
-      <c r="D101" s="101"/>
-      <c r="E101" s="101"/>
-      <c r="F101" s="101"/>
-      <c r="G101" s="101"/>
-      <c r="H101" s="101"/>
-      <c r="I101" s="101"/>
-      <c r="J101" s="101"/>
-      <c r="K101" s="101"/>
-      <c r="L101" s="73"/>
-      <c r="M101" s="73"/>
-      <c r="N101" s="73"/>
-      <c r="O101" s="73"/>
-      <c r="P101" s="73"/>
+      <c r="B101" s="105"/>
+      <c r="C101" s="106"/>
+      <c r="D101" s="106"/>
+      <c r="E101" s="106"/>
+      <c r="F101" s="106"/>
+      <c r="G101" s="106"/>
+      <c r="H101" s="106"/>
+      <c r="I101" s="106"/>
+      <c r="J101" s="106"/>
+      <c r="K101" s="106"/>
+      <c r="L101" s="79"/>
+      <c r="M101" s="79"/>
+      <c r="N101" s="79"/>
+      <c r="O101" s="79"/>
+      <c r="P101" s="79"/>
       <c r="Q101" s="40"/>
       <c r="R101" s="41"/>
-      <c r="T101" s="62"/>
-      <c r="U101" s="70" t="s">
-        <v>179</v>
+      <c r="T101" s="68"/>
+      <c r="U101" s="76" t="s">
+        <v>168</v>
       </c>
       <c r="V101" s="11"/>
-      <c r="W101" s="64"/>
+      <c r="W101" s="70"/>
     </row>
     <row r="102" spans="2:23" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="95" t="s">
-        <v>168</v>
-      </c>
-      <c r="C102" s="96"/>
-      <c r="D102" s="96"/>
-      <c r="E102" s="96"/>
-      <c r="F102" s="96"/>
-      <c r="G102" s="96"/>
-      <c r="H102" s="96"/>
-      <c r="I102" s="96"/>
-      <c r="J102" s="96"/>
-      <c r="K102" s="96"/>
-      <c r="L102" s="96"/>
-      <c r="M102" s="96" t="s">
-        <v>188</v>
-      </c>
-      <c r="N102" s="96"/>
-      <c r="O102" s="96"/>
-      <c r="P102" s="96"/>
-      <c r="Q102" s="96"/>
-      <c r="R102" s="97"/>
-      <c r="T102" s="62"/>
-      <c r="U102" s="71" t="s">
-        <v>189</v>
+      <c r="B102" s="100" t="s">
+        <v>163</v>
+      </c>
+      <c r="C102" s="101"/>
+      <c r="D102" s="101"/>
+      <c r="E102" s="101"/>
+      <c r="F102" s="101"/>
+      <c r="G102" s="101"/>
+      <c r="H102" s="101"/>
+      <c r="I102" s="101"/>
+      <c r="J102" s="101"/>
+      <c r="K102" s="101"/>
+      <c r="L102" s="101"/>
+      <c r="M102" s="101" t="s">
+        <v>175</v>
+      </c>
+      <c r="N102" s="101"/>
+      <c r="O102" s="101"/>
+      <c r="P102" s="101"/>
+      <c r="Q102" s="101"/>
+      <c r="R102" s="102"/>
+      <c r="T102" s="68"/>
+      <c r="U102" s="77" t="s">
+        <v>176</v>
       </c>
       <c r="V102" s="11"/>
-      <c r="W102" s="64"/>
+      <c r="W102" s="70"/>
     </row>
     <row r="103" spans="2:23" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B103" s="102"/>
-      <c r="C103" s="103"/>
-      <c r="D103" s="103"/>
-      <c r="E103" s="103"/>
-      <c r="F103" s="103"/>
-      <c r="G103" s="103"/>
-      <c r="H103" s="103"/>
-      <c r="I103" s="103"/>
-      <c r="J103" s="103"/>
-      <c r="K103" s="103"/>
-      <c r="L103" s="103"/>
-      <c r="M103" s="103"/>
-      <c r="N103" s="103"/>
-      <c r="O103" s="103"/>
-      <c r="P103" s="103"/>
-      <c r="Q103" s="103"/>
-      <c r="R103" s="108"/>
-      <c r="T103" s="62"/>
-      <c r="U103" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="V103" s="69"/>
-      <c r="W103" s="64"/>
+      <c r="B103" s="107"/>
+      <c r="C103" s="108"/>
+      <c r="D103" s="108"/>
+      <c r="E103" s="108"/>
+      <c r="F103" s="108"/>
+      <c r="G103" s="108"/>
+      <c r="H103" s="108"/>
+      <c r="I103" s="108"/>
+      <c r="J103" s="108"/>
+      <c r="K103" s="108"/>
+      <c r="L103" s="108"/>
+      <c r="M103" s="108"/>
+      <c r="N103" s="108"/>
+      <c r="O103" s="108"/>
+      <c r="P103" s="108"/>
+      <c r="Q103" s="108"/>
+      <c r="R103" s="113"/>
+      <c r="T103" s="68"/>
+      <c r="U103" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="V103" s="75"/>
+      <c r="W103" s="70"/>
     </row>
     <row r="104" spans="2:23" ht="170.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="104"/>
-      <c r="C104" s="105"/>
-      <c r="D104" s="105"/>
-      <c r="E104" s="105"/>
-      <c r="F104" s="105"/>
-      <c r="G104" s="105"/>
-      <c r="H104" s="105"/>
-      <c r="I104" s="105"/>
-      <c r="J104" s="105"/>
-      <c r="K104" s="105"/>
-      <c r="L104" s="105"/>
-      <c r="M104" s="105"/>
-      <c r="N104" s="105"/>
-      <c r="O104" s="105"/>
-      <c r="P104" s="105"/>
-      <c r="Q104" s="105"/>
-      <c r="R104" s="109"/>
-      <c r="T104" s="74"/>
-      <c r="U104" s="75"/>
-      <c r="V104" s="75"/>
-      <c r="W104" s="76"/>
+      <c r="B104" s="109"/>
+      <c r="C104" s="110"/>
+      <c r="D104" s="110"/>
+      <c r="E104" s="110"/>
+      <c r="F104" s="110"/>
+      <c r="G104" s="110"/>
+      <c r="H104" s="110"/>
+      <c r="I104" s="110"/>
+      <c r="J104" s="110"/>
+      <c r="K104" s="110"/>
+      <c r="L104" s="110"/>
+      <c r="M104" s="110"/>
+      <c r="N104" s="110"/>
+      <c r="O104" s="110"/>
+      <c r="P104" s="110"/>
+      <c r="Q104" s="110"/>
+      <c r="R104" s="114"/>
+      <c r="T104" s="80"/>
+      <c r="U104" s="81"/>
+      <c r="V104" s="81"/>
+      <c r="W104" s="82"/>
     </row>
     <row r="105" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B105" s="104"/>
-      <c r="C105" s="105"/>
-      <c r="D105" s="105"/>
-      <c r="E105" s="105"/>
-      <c r="F105" s="105"/>
-      <c r="G105" s="105"/>
-      <c r="H105" s="105"/>
-      <c r="I105" s="105"/>
-      <c r="J105" s="105"/>
-      <c r="K105" s="105"/>
-      <c r="L105" s="105"/>
-      <c r="M105" s="105"/>
-      <c r="N105" s="105"/>
-      <c r="O105" s="105"/>
-      <c r="P105" s="105"/>
-      <c r="Q105" s="105"/>
-      <c r="R105" s="109"/>
+      <c r="B105" s="109"/>
+      <c r="C105" s="110"/>
+      <c r="D105" s="110"/>
+      <c r="E105" s="110"/>
+      <c r="F105" s="110"/>
+      <c r="G105" s="110"/>
+      <c r="H105" s="110"/>
+      <c r="I105" s="110"/>
+      <c r="J105" s="110"/>
+      <c r="K105" s="110"/>
+      <c r="L105" s="110"/>
+      <c r="M105" s="110"/>
+      <c r="N105" s="110"/>
+      <c r="O105" s="110"/>
+      <c r="P105" s="110"/>
+      <c r="Q105" s="110"/>
+      <c r="R105" s="114"/>
     </row>
     <row r="106" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B106" s="104"/>
-      <c r="C106" s="105"/>
-      <c r="D106" s="105"/>
-      <c r="E106" s="105"/>
-      <c r="F106" s="105"/>
-      <c r="G106" s="105"/>
-      <c r="H106" s="105"/>
-      <c r="I106" s="105"/>
-      <c r="J106" s="105"/>
-      <c r="K106" s="105"/>
-      <c r="L106" s="105"/>
-      <c r="M106" s="105"/>
-      <c r="N106" s="105"/>
-      <c r="O106" s="105"/>
-      <c r="P106" s="105"/>
-      <c r="Q106" s="105"/>
-      <c r="R106" s="109"/>
+      <c r="B106" s="109"/>
+      <c r="C106" s="110"/>
+      <c r="D106" s="110"/>
+      <c r="E106" s="110"/>
+      <c r="F106" s="110"/>
+      <c r="G106" s="110"/>
+      <c r="H106" s="110"/>
+      <c r="I106" s="110"/>
+      <c r="J106" s="110"/>
+      <c r="K106" s="110"/>
+      <c r="L106" s="110"/>
+      <c r="M106" s="110"/>
+      <c r="N106" s="110"/>
+      <c r="O106" s="110"/>
+      <c r="P106" s="110"/>
+      <c r="Q106" s="110"/>
+      <c r="R106" s="114"/>
     </row>
     <row r="107" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B107" s="104"/>
-      <c r="C107" s="105"/>
-      <c r="D107" s="105"/>
-      <c r="E107" s="105"/>
-      <c r="F107" s="105"/>
-      <c r="G107" s="105"/>
-      <c r="H107" s="105"/>
-      <c r="I107" s="105"/>
-      <c r="J107" s="105"/>
-      <c r="K107" s="105"/>
-      <c r="L107" s="105"/>
-      <c r="M107" s="105"/>
-      <c r="N107" s="105"/>
-      <c r="O107" s="105"/>
-      <c r="P107" s="105"/>
-      <c r="Q107" s="105"/>
-      <c r="R107" s="109"/>
+      <c r="B107" s="109"/>
+      <c r="C107" s="110"/>
+      <c r="D107" s="110"/>
+      <c r="E107" s="110"/>
+      <c r="F107" s="110"/>
+      <c r="G107" s="110"/>
+      <c r="H107" s="110"/>
+      <c r="I107" s="110"/>
+      <c r="J107" s="110"/>
+      <c r="K107" s="110"/>
+      <c r="L107" s="110"/>
+      <c r="M107" s="110"/>
+      <c r="N107" s="110"/>
+      <c r="O107" s="110"/>
+      <c r="P107" s="110"/>
+      <c r="Q107" s="110"/>
+      <c r="R107" s="114"/>
     </row>
     <row r="108" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="106"/>
-      <c r="C108" s="107"/>
-      <c r="D108" s="107"/>
-      <c r="E108" s="107"/>
-      <c r="F108" s="107"/>
-      <c r="G108" s="107"/>
-      <c r="H108" s="107"/>
-      <c r="I108" s="107"/>
-      <c r="J108" s="107"/>
-      <c r="K108" s="107"/>
-      <c r="L108" s="107"/>
-      <c r="M108" s="107"/>
-      <c r="N108" s="107"/>
-      <c r="O108" s="107"/>
-      <c r="P108" s="107"/>
-      <c r="Q108" s="107"/>
-      <c r="R108" s="110"/>
+      <c r="B108" s="111"/>
+      <c r="C108" s="112"/>
+      <c r="D108" s="112"/>
+      <c r="E108" s="112"/>
+      <c r="F108" s="112"/>
+      <c r="G108" s="112"/>
+      <c r="H108" s="112"/>
+      <c r="I108" s="112"/>
+      <c r="J108" s="112"/>
+      <c r="K108" s="112"/>
+      <c r="L108" s="112"/>
+      <c r="M108" s="112"/>
+      <c r="N108" s="112"/>
+      <c r="O108" s="112"/>
+      <c r="P108" s="112"/>
+      <c r="Q108" s="112"/>
+      <c r="R108" s="115"/>
     </row>
     <row r="109" spans="2:23" ht="158.1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -6278,11 +5760,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:R19">
-    <cfRule type="expression" dxfId="32" priority="33">
+    <cfRule type="expression" dxfId="32" priority="34">
+      <formula>$D$13="FIRST BOX"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="33">
       <formula>$D$13="BEP"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="34">
-      <formula>$D$13="FIRST BOX"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:D22">
@@ -6291,11 +5773,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5">
-    <cfRule type="expression" dxfId="29" priority="23">
+    <cfRule type="expression" dxfId="29" priority="24">
+      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="23">
       <formula>AND(#REF!="LAST DROP",$F$47="ΝΑΙ")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="24">
-      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13:F13">
@@ -6304,11 +5786,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:G18 D13:F13 C22:D22">
-    <cfRule type="expression" dxfId="26" priority="31">
+    <cfRule type="expression" dxfId="26" priority="32">
+      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="31">
       <formula>AND(#REF!="LAST DROP",$F$47="ΝΑΙ")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="32">
-      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:G18">
@@ -6317,91 +5799,91 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="containsBlanks" dxfId="23" priority="19">
-      <formula>LEN(TRIM(F5))=0</formula>
+    <cfRule type="expression" dxfId="23" priority="21">
+      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="20">
       <formula>AND(#REF!="LAST DROP",$F$47="ΝΑΙ")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="21">
-      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
+    <cfRule type="containsBlanks" dxfId="21" priority="19">
+      <formula>LEN(TRIM(F5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P25:Q39">
-    <cfRule type="containsBlanks" dxfId="20" priority="25">
-      <formula>LEN(TRIM(P25))=0</formula>
+    <cfRule type="expression" dxfId="20" priority="27">
+      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="26">
       <formula>AND(#REF!="LAST DROP",$F$47="ΝΑΙ")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="27">
-      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
+    <cfRule type="containsBlanks" dxfId="18" priority="25">
+      <formula>LEN(TRIM(P25))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5">
-    <cfRule type="containsBlanks" dxfId="17" priority="16">
-      <formula>LEN(TRIM(R5))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="17">
+    <cfRule type="expression" dxfId="17" priority="17">
       <formula>AND(#REF!="LAST DROP",$F$47="ΝΑΙ")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="18">
+    <cfRule type="expression" dxfId="16" priority="18">
       <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="15" priority="16">
+      <formula>LEN(TRIM(R5))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V83">
-    <cfRule type="containsBlanks" dxfId="14" priority="1">
-      <formula>LEN(TRIM(V83))=0</formula>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
       <formula>AND(#REF!="LAST DROP",$F$47="ΝΑΙ")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="3">
-      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
+    <cfRule type="containsBlanks" dxfId="12" priority="1">
+      <formula>LEN(TRIM(V83))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V86:V87">
-    <cfRule type="containsBlanks" dxfId="11" priority="13">
+    <cfRule type="expression" dxfId="11" priority="14">
+      <formula>AND(#REF!="LAST DROP",$F$47="ΝΑΙ")</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="10" priority="13">
       <formula>LEN(TRIM(V86))=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="14">
-      <formula>AND(#REF!="LAST DROP",$F$47="ΝΑΙ")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="15">
       <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V90:V93">
-    <cfRule type="containsBlanks" dxfId="8" priority="10">
-      <formula>LEN(TRIM(V90))=0</formula>
+    <cfRule type="expression" dxfId="8" priority="12">
+      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="11">
       <formula>AND(#REF!="LAST DROP",$F$47="ΝΑΙ")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="12">
-      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
+    <cfRule type="containsBlanks" dxfId="6" priority="10">
+      <formula>LEN(TRIM(V90))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V96">
-    <cfRule type="containsBlanks" dxfId="5" priority="7">
-      <formula>LEN(TRIM(V96))=0</formula>
+    <cfRule type="expression" dxfId="5" priority="9">
+      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="8">
       <formula>AND(#REF!="LAST DROP",$F$47="ΝΑΙ")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="9">
-      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
+    <cfRule type="containsBlanks" dxfId="3" priority="7">
+      <formula>LEN(TRIM(V96))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V99:V103">
-    <cfRule type="containsBlanks" dxfId="2" priority="4">
-      <formula>LEN(TRIM(V99))=0</formula>
+    <cfRule type="expression" dxfId="2" priority="6">
+      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="5">
       <formula>AND(#REF!="LAST DROP",$F$47="ΝΑΙ")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6">
-      <formula>AND(#REF!="LAST DROP",$F$47&lt;&gt;"ΝΑΙ")</formula>
+    <cfRule type="containsBlanks" dxfId="0" priority="4">
+      <formula>LEN(TRIM(V99))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
@@ -6434,6 +5916,5 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>